--- a/DVOL_data.xlsx
+++ b/DVOL_data.xlsx
@@ -471,666 +471,666 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>1744502400000</v>
+        <v>1744416000000</v>
       </c>
       <c r="B2" t="n">
+        <v>56.15</v>
+      </c>
+      <c r="C2" t="n">
+        <v>57.52</v>
+      </c>
+      <c r="D2" t="n">
+        <v>55.35</v>
+      </c>
+      <c r="E2" t="n">
         <v>57.45</v>
       </c>
-      <c r="C2" t="n">
-        <v>57.76</v>
-      </c>
-      <c r="D2" t="n">
-        <v>55.17</v>
-      </c>
-      <c r="E2" t="n">
-        <v>56.29</v>
-      </c>
       <c r="F2" s="2" t="n">
-        <v>45760</v>
+        <v>45759</v>
       </c>
       <c r="G2" t="n">
-        <v>0.31685641</v>
+        <v>0.33005025</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>1744588800000</v>
+        <v>1744502400000</v>
       </c>
       <c r="B3" t="n">
+        <v>57.45</v>
+      </c>
+      <c r="C3" t="n">
+        <v>57.76</v>
+      </c>
+      <c r="D3" t="n">
+        <v>55.17</v>
+      </c>
+      <c r="E3" t="n">
         <v>56.29</v>
       </c>
-      <c r="C3" t="n">
-        <v>56.4</v>
-      </c>
-      <c r="D3" t="n">
-        <v>52.34</v>
-      </c>
-      <c r="E3" t="n">
-        <v>53.31</v>
-      </c>
       <c r="F3" s="2" t="n">
-        <v>45761</v>
+        <v>45760</v>
       </c>
       <c r="G3" t="n">
-        <v>0.28419561</v>
+        <v>0.31685641</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>1744675200000</v>
+        <v>1744588800000</v>
       </c>
       <c r="B4" t="n">
-        <v>52.02</v>
+        <v>56.29</v>
       </c>
       <c r="C4" t="n">
-        <v>52.4</v>
+        <v>56.4</v>
       </c>
       <c r="D4" t="n">
-        <v>49.97</v>
+        <v>52.34</v>
       </c>
       <c r="E4" t="n">
-        <v>50.39</v>
+        <v>53.31</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>45762</v>
+        <v>45761</v>
       </c>
       <c r="G4" t="n">
-        <v>0.25391521</v>
+        <v>0.28419561</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>1744761600000</v>
+        <v>1744675200000</v>
       </c>
       <c r="B5" t="n">
+        <v>52.02</v>
+      </c>
+      <c r="C5" t="n">
+        <v>52.4</v>
+      </c>
+      <c r="D5" t="n">
+        <v>49.97</v>
+      </c>
+      <c r="E5" t="n">
         <v>50.39</v>
       </c>
-      <c r="C5" t="n">
-        <v>50.56</v>
-      </c>
-      <c r="D5" t="n">
-        <v>49</v>
-      </c>
-      <c r="E5" t="n">
-        <v>49.58</v>
-      </c>
       <c r="F5" s="2" t="n">
-        <v>45763</v>
+        <v>45762</v>
       </c>
       <c r="G5" t="n">
-        <v>0.24581764</v>
+        <v>0.25391521</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>1744848000000</v>
+        <v>1744761600000</v>
       </c>
       <c r="B6" t="n">
+        <v>50.39</v>
+      </c>
+      <c r="C6" t="n">
+        <v>50.56</v>
+      </c>
+      <c r="D6" t="n">
+        <v>49</v>
+      </c>
+      <c r="E6" t="n">
         <v>49.58</v>
       </c>
-      <c r="C6" t="n">
-        <v>49.63</v>
-      </c>
-      <c r="D6" t="n">
-        <v>48.28</v>
-      </c>
-      <c r="E6" t="n">
-        <v>48.41</v>
-      </c>
       <c r="F6" s="2" t="n">
-        <v>45764</v>
+        <v>45763</v>
       </c>
       <c r="G6" t="n">
-        <v>0.23435281</v>
+        <v>0.24581764</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>1744934400000</v>
+        <v>1744848000000</v>
       </c>
       <c r="B7" t="n">
+        <v>49.58</v>
+      </c>
+      <c r="C7" t="n">
+        <v>49.63</v>
+      </c>
+      <c r="D7" t="n">
+        <v>48.28</v>
+      </c>
+      <c r="E7" t="n">
         <v>48.41</v>
       </c>
-      <c r="C7" t="n">
-        <v>48.44</v>
-      </c>
-      <c r="D7" t="n">
-        <v>46.41</v>
-      </c>
-      <c r="E7" t="n">
-        <v>46.9</v>
-      </c>
       <c r="F7" s="2" t="n">
-        <v>45765</v>
+        <v>45764</v>
       </c>
       <c r="G7" t="n">
-        <v>0.219961</v>
+        <v>0.23435281</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>1745020800000</v>
+        <v>1744934400000</v>
       </c>
       <c r="B8" t="n">
+        <v>48.41</v>
+      </c>
+      <c r="C8" t="n">
+        <v>48.44</v>
+      </c>
+      <c r="D8" t="n">
+        <v>46.41</v>
+      </c>
+      <c r="E8" t="n">
         <v>46.9</v>
       </c>
-      <c r="C8" t="n">
-        <v>48.43</v>
-      </c>
-      <c r="D8" t="n">
-        <v>46.83</v>
-      </c>
-      <c r="E8" t="n">
-        <v>48.29</v>
-      </c>
       <c r="F8" s="2" t="n">
-        <v>45766</v>
+        <v>45765</v>
       </c>
       <c r="G8" t="n">
-        <v>0.23319241</v>
+        <v>0.219961</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>1745107200000</v>
+        <v>1745020800000</v>
       </c>
       <c r="B9" t="n">
-        <v>48.3</v>
+        <v>46.9</v>
       </c>
       <c r="C9" t="n">
-        <v>48.46</v>
+        <v>48.43</v>
       </c>
       <c r="D9" t="n">
-        <v>47.71</v>
+        <v>46.83</v>
       </c>
       <c r="E9" t="n">
-        <v>48.2</v>
+        <v>48.29</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>45767</v>
+        <v>45766</v>
       </c>
       <c r="G9" t="n">
-        <v>0.232324</v>
+        <v>0.23319241</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>1745193600000</v>
+        <v>1745107200000</v>
       </c>
       <c r="B10" t="n">
+        <v>48.3</v>
+      </c>
+      <c r="C10" t="n">
+        <v>48.46</v>
+      </c>
+      <c r="D10" t="n">
+        <v>47.71</v>
+      </c>
+      <c r="E10" t="n">
         <v>48.2</v>
       </c>
-      <c r="C10" t="n">
-        <v>50.71</v>
-      </c>
-      <c r="D10" t="n">
-        <v>48.2</v>
-      </c>
-      <c r="E10" t="n">
-        <v>49.16</v>
-      </c>
       <c r="F10" s="2" t="n">
-        <v>45768</v>
+        <v>45767</v>
       </c>
       <c r="G10" t="n">
-        <v>0.24167056</v>
+        <v>0.232324</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>1745280000000</v>
+        <v>1745193600000</v>
       </c>
       <c r="B11" t="n">
+        <v>48.2</v>
+      </c>
+      <c r="C11" t="n">
+        <v>50.71</v>
+      </c>
+      <c r="D11" t="n">
+        <v>48.2</v>
+      </c>
+      <c r="E11" t="n">
         <v>49.16</v>
       </c>
-      <c r="C11" t="n">
-        <v>52.71</v>
-      </c>
-      <c r="D11" t="n">
-        <v>49</v>
-      </c>
-      <c r="E11" t="n">
-        <v>52.69</v>
-      </c>
       <c r="F11" s="2" t="n">
-        <v>45769</v>
+        <v>45768</v>
       </c>
       <c r="G11" t="n">
-        <v>0.2776236099999999</v>
+        <v>0.24167056</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>1745366400000</v>
+        <v>1745280000000</v>
       </c>
       <c r="B12" t="n">
+        <v>49.16</v>
+      </c>
+      <c r="C12" t="n">
+        <v>52.71</v>
+      </c>
+      <c r="D12" t="n">
+        <v>49</v>
+      </c>
+      <c r="E12" t="n">
         <v>52.69</v>
       </c>
-      <c r="C12" t="n">
-        <v>52.86</v>
-      </c>
-      <c r="D12" t="n">
-        <v>49.4</v>
-      </c>
-      <c r="E12" t="n">
-        <v>49.42</v>
-      </c>
       <c r="F12" s="2" t="n">
-        <v>45770</v>
+        <v>45769</v>
       </c>
       <c r="G12" t="n">
-        <v>0.24423364</v>
+        <v>0.2776236099999999</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>1745452800000</v>
+        <v>1745366400000</v>
       </c>
       <c r="B13" t="n">
+        <v>52.69</v>
+      </c>
+      <c r="C13" t="n">
+        <v>52.86</v>
+      </c>
+      <c r="D13" t="n">
+        <v>49.4</v>
+      </c>
+      <c r="E13" t="n">
         <v>49.42</v>
       </c>
-      <c r="C13" t="n">
-        <v>49.42</v>
-      </c>
-      <c r="D13" t="n">
-        <v>46.66</v>
-      </c>
-      <c r="E13" t="n">
-        <v>46.96</v>
-      </c>
       <c r="F13" s="2" t="n">
-        <v>45771</v>
+        <v>45770</v>
       </c>
       <c r="G13" t="n">
-        <v>0.22052416</v>
+        <v>0.24423364</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>1745539200000</v>
+        <v>1745452800000</v>
       </c>
       <c r="B14" t="n">
+        <v>49.42</v>
+      </c>
+      <c r="C14" t="n">
+        <v>49.42</v>
+      </c>
+      <c r="D14" t="n">
+        <v>46.66</v>
+      </c>
+      <c r="E14" t="n">
         <v>46.96</v>
       </c>
-      <c r="C14" t="n">
-        <v>48.71</v>
-      </c>
-      <c r="D14" t="n">
-        <v>46.44</v>
-      </c>
-      <c r="E14" t="n">
-        <v>46.45</v>
-      </c>
       <c r="F14" s="2" t="n">
-        <v>45772</v>
+        <v>45771</v>
       </c>
       <c r="G14" t="n">
-        <v>0.21576025</v>
+        <v>0.22052416</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>1745625600000</v>
+        <v>1745539200000</v>
       </c>
       <c r="B15" t="n">
+        <v>46.96</v>
+      </c>
+      <c r="C15" t="n">
+        <v>48.71</v>
+      </c>
+      <c r="D15" t="n">
+        <v>46.44</v>
+      </c>
+      <c r="E15" t="n">
         <v>46.45</v>
       </c>
-      <c r="C15" t="n">
-        <v>47.64</v>
-      </c>
-      <c r="D15" t="n">
-        <v>46.08</v>
-      </c>
-      <c r="E15" t="n">
-        <v>47.42</v>
-      </c>
       <c r="F15" s="2" t="n">
-        <v>45773</v>
+        <v>45772</v>
       </c>
       <c r="G15" t="n">
-        <v>0.22486564</v>
+        <v>0.21576025</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>1745712000000</v>
+        <v>1745625600000</v>
       </c>
       <c r="B16" t="n">
+        <v>46.45</v>
+      </c>
+      <c r="C16" t="n">
+        <v>47.64</v>
+      </c>
+      <c r="D16" t="n">
+        <v>46.08</v>
+      </c>
+      <c r="E16" t="n">
         <v>47.42</v>
       </c>
-      <c r="C16" t="n">
-        <v>48.35</v>
-      </c>
-      <c r="D16" t="n">
-        <v>47.33</v>
-      </c>
-      <c r="E16" t="n">
-        <v>48.12</v>
-      </c>
       <c r="F16" s="2" t="n">
-        <v>45774</v>
+        <v>45773</v>
       </c>
       <c r="G16" t="n">
-        <v>0.23155344</v>
+        <v>0.22486564</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>1745798400000</v>
+        <v>1745712000000</v>
       </c>
       <c r="B17" t="n">
+        <v>47.42</v>
+      </c>
+      <c r="C17" t="n">
+        <v>48.35</v>
+      </c>
+      <c r="D17" t="n">
+        <v>47.33</v>
+      </c>
+      <c r="E17" t="n">
         <v>48.12</v>
       </c>
-      <c r="C17" t="n">
-        <v>48.61</v>
-      </c>
-      <c r="D17" t="n">
-        <v>46.38</v>
-      </c>
-      <c r="E17" t="n">
-        <v>47.05</v>
-      </c>
       <c r="F17" s="2" t="n">
-        <v>45775</v>
+        <v>45774</v>
       </c>
       <c r="G17" t="n">
-        <v>0.22137025</v>
+        <v>0.23155344</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>1745884800000</v>
+        <v>1745798400000</v>
       </c>
       <c r="B18" t="n">
+        <v>48.12</v>
+      </c>
+      <c r="C18" t="n">
+        <v>48.61</v>
+      </c>
+      <c r="D18" t="n">
+        <v>46.38</v>
+      </c>
+      <c r="E18" t="n">
         <v>47.05</v>
       </c>
-      <c r="C18" t="n">
-        <v>47.24</v>
-      </c>
-      <c r="D18" t="n">
-        <v>46.04</v>
-      </c>
-      <c r="E18" t="n">
-        <v>46.17</v>
-      </c>
       <c r="F18" s="2" t="n">
-        <v>45776</v>
+        <v>45775</v>
       </c>
       <c r="G18" t="n">
-        <v>0.21316689</v>
+        <v>0.22137025</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>1745971200000</v>
+        <v>1745884800000</v>
       </c>
       <c r="B19" t="n">
+        <v>47.05</v>
+      </c>
+      <c r="C19" t="n">
+        <v>47.24</v>
+      </c>
+      <c r="D19" t="n">
+        <v>46.04</v>
+      </c>
+      <c r="E19" t="n">
         <v>46.17</v>
       </c>
-      <c r="C19" t="n">
-        <v>46.79</v>
-      </c>
-      <c r="D19" t="n">
-        <v>45.02</v>
-      </c>
-      <c r="E19" t="n">
-        <v>45.07</v>
-      </c>
       <c r="F19" s="2" t="n">
-        <v>45777</v>
+        <v>45776</v>
       </c>
       <c r="G19" t="n">
-        <v>0.20313049</v>
+        <v>0.21316689</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>1746057600000</v>
+        <v>1745971200000</v>
       </c>
       <c r="B20" t="n">
+        <v>46.17</v>
+      </c>
+      <c r="C20" t="n">
+        <v>46.79</v>
+      </c>
+      <c r="D20" t="n">
+        <v>45.02</v>
+      </c>
+      <c r="E20" t="n">
         <v>45.07</v>
       </c>
-      <c r="C20" t="n">
-        <v>46.97</v>
-      </c>
-      <c r="D20" t="n">
-        <v>44.74</v>
-      </c>
-      <c r="E20" t="n">
-        <v>46.11</v>
-      </c>
       <c r="F20" s="2" t="n">
-        <v>45778</v>
+        <v>45777</v>
       </c>
       <c r="G20" t="n">
-        <v>0.21261321</v>
+        <v>0.20313049</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>1746144000000</v>
+        <v>1746057600000</v>
       </c>
       <c r="B21" t="n">
+        <v>45.07</v>
+      </c>
+      <c r="C21" t="n">
+        <v>46.97</v>
+      </c>
+      <c r="D21" t="n">
+        <v>44.74</v>
+      </c>
+      <c r="E21" t="n">
         <v>46.11</v>
       </c>
-      <c r="C21" t="n">
-        <v>48.1</v>
-      </c>
-      <c r="D21" t="n">
-        <v>44.38</v>
-      </c>
-      <c r="E21" t="n">
-        <v>44.54</v>
-      </c>
       <c r="F21" s="2" t="n">
-        <v>45779</v>
+        <v>45778</v>
       </c>
       <c r="G21" t="n">
-        <v>0.19838116</v>
+        <v>0.21261321</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>1746230400000</v>
+        <v>1746144000000</v>
       </c>
       <c r="B22" t="n">
+        <v>46.11</v>
+      </c>
+      <c r="C22" t="n">
+        <v>48.1</v>
+      </c>
+      <c r="D22" t="n">
+        <v>44.38</v>
+      </c>
+      <c r="E22" t="n">
         <v>44.54</v>
       </c>
-      <c r="C22" t="n">
-        <v>45.41</v>
-      </c>
-      <c r="D22" t="n">
-        <v>44.2</v>
-      </c>
-      <c r="E22" t="n">
-        <v>44.9</v>
-      </c>
       <c r="F22" s="2" t="n">
-        <v>45780</v>
+        <v>45779</v>
       </c>
       <c r="G22" t="n">
-        <v>0.201601</v>
+        <v>0.19838116</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>1746316800000</v>
+        <v>1746230400000</v>
       </c>
       <c r="B23" t="n">
+        <v>44.54</v>
+      </c>
+      <c r="C23" t="n">
+        <v>45.41</v>
+      </c>
+      <c r="D23" t="n">
+        <v>44.2</v>
+      </c>
+      <c r="E23" t="n">
         <v>44.9</v>
       </c>
-      <c r="C23" t="n">
-        <v>46.38</v>
-      </c>
-      <c r="D23" t="n">
-        <v>44.73</v>
-      </c>
-      <c r="E23" t="n">
-        <v>46.35</v>
-      </c>
       <c r="F23" s="2" t="n">
-        <v>45781</v>
+        <v>45780</v>
       </c>
       <c r="G23" t="n">
-        <v>0.21483225</v>
+        <v>0.201601</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>1746403200000</v>
+        <v>1746316800000</v>
       </c>
       <c r="B24" t="n">
+        <v>44.9</v>
+      </c>
+      <c r="C24" t="n">
+        <v>46.38</v>
+      </c>
+      <c r="D24" t="n">
+        <v>44.73</v>
+      </c>
+      <c r="E24" t="n">
         <v>46.35</v>
       </c>
-      <c r="C24" t="n">
-        <v>46.87</v>
-      </c>
-      <c r="D24" t="n">
-        <v>44.89</v>
-      </c>
-      <c r="E24" t="n">
-        <v>45</v>
-      </c>
       <c r="F24" s="2" t="n">
-        <v>45782</v>
+        <v>45781</v>
       </c>
       <c r="G24" t="n">
-        <v>0.2025</v>
+        <v>0.21483225</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>1746489600000</v>
+        <v>1746403200000</v>
       </c>
       <c r="B25" t="n">
+        <v>46.35</v>
+      </c>
+      <c r="C25" t="n">
+        <v>46.87</v>
+      </c>
+      <c r="D25" t="n">
+        <v>44.89</v>
+      </c>
+      <c r="E25" t="n">
         <v>45</v>
       </c>
-      <c r="C25" t="n">
-        <v>46.66</v>
-      </c>
-      <c r="D25" t="n">
-        <v>44.86</v>
-      </c>
-      <c r="E25" t="n">
-        <v>46.66</v>
-      </c>
       <c r="F25" s="2" t="n">
-        <v>45783</v>
+        <v>45782</v>
       </c>
       <c r="G25" t="n">
-        <v>0.21771556</v>
+        <v>0.2025</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>1746576000000</v>
+        <v>1746489600000</v>
       </c>
       <c r="B26" t="n">
+        <v>45</v>
+      </c>
+      <c r="C26" t="n">
         <v>46.66</v>
       </c>
-      <c r="C26" t="n">
-        <v>47.26</v>
-      </c>
       <c r="D26" t="n">
-        <v>44.59</v>
+        <v>44.86</v>
       </c>
       <c r="E26" t="n">
-        <v>44.8</v>
+        <v>46.66</v>
       </c>
       <c r="F26" s="2" t="n">
-        <v>45784</v>
+        <v>45783</v>
       </c>
       <c r="G26" t="n">
-        <v>0.200704</v>
+        <v>0.21771556</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>1746662400000</v>
+        <v>1746576000000</v>
       </c>
       <c r="B27" t="n">
+        <v>46.66</v>
+      </c>
+      <c r="C27" t="n">
+        <v>47.26</v>
+      </c>
+      <c r="D27" t="n">
+        <v>44.59</v>
+      </c>
+      <c r="E27" t="n">
         <v>44.8</v>
       </c>
-      <c r="C27" t="n">
-        <v>47.17</v>
-      </c>
-      <c r="D27" t="n">
-        <v>44.55</v>
-      </c>
-      <c r="E27" t="n">
-        <v>45.88</v>
-      </c>
       <c r="F27" s="2" t="n">
-        <v>45785</v>
+        <v>45784</v>
       </c>
       <c r="G27" t="n">
-        <v>0.21049744</v>
+        <v>0.200704</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>1746748800000</v>
+        <v>1746662400000</v>
       </c>
       <c r="B28" t="n">
+        <v>44.8</v>
+      </c>
+      <c r="C28" t="n">
+        <v>47.17</v>
+      </c>
+      <c r="D28" t="n">
+        <v>44.55</v>
+      </c>
+      <c r="E28" t="n">
         <v>45.88</v>
       </c>
-      <c r="C28" t="n">
-        <v>46.36</v>
-      </c>
-      <c r="D28" t="n">
-        <v>45.21</v>
-      </c>
-      <c r="E28" t="n">
-        <v>45.78</v>
-      </c>
       <c r="F28" s="2" t="n">
-        <v>45786</v>
+        <v>45785</v>
       </c>
       <c r="G28" t="n">
-        <v>0.20958084</v>
+        <v>0.21049744</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>1746835200000</v>
+        <v>1746748800000</v>
       </c>
       <c r="B29" t="n">
+        <v>45.88</v>
+      </c>
+      <c r="C29" t="n">
+        <v>46.36</v>
+      </c>
+      <c r="D29" t="n">
+        <v>45.21</v>
+      </c>
+      <c r="E29" t="n">
         <v>45.78</v>
       </c>
-      <c r="C29" t="n">
-        <v>47.59</v>
-      </c>
-      <c r="D29" t="n">
-        <v>45.6</v>
-      </c>
-      <c r="E29" t="n">
-        <v>47.13</v>
-      </c>
       <c r="F29" s="2" t="n">
-        <v>45787</v>
+        <v>45786</v>
       </c>
       <c r="G29" t="n">
-        <v>0.22212369</v>
+        <v>0.20958084</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>1746921600000</v>
+        <v>1746835200000</v>
       </c>
       <c r="B30" t="n">
-        <v>47.13</v>
+        <v>45.78</v>
       </c>
       <c r="C30" t="n">
-        <v>48.34</v>
+        <v>47.59</v>
       </c>
       <c r="D30" t="n">
-        <v>46.06</v>
+        <v>45.6</v>
       </c>
       <c r="E30" t="n">
         <v>47.13</v>
       </c>
       <c r="F30" s="2" t="n">
-        <v>45788</v>
+        <v>45787</v>
       </c>
       <c r="G30" t="n">
         <v>0.22212369</v>
@@ -1138,3357 +1138,3357 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>1747008000000</v>
+        <v>1746921600000</v>
       </c>
       <c r="B31" t="n">
         <v>47.13</v>
       </c>
       <c r="C31" t="n">
-        <v>48.45</v>
+        <v>48.34</v>
       </c>
       <c r="D31" t="n">
-        <v>45.29</v>
+        <v>46.06</v>
       </c>
       <c r="E31" t="n">
-        <v>45.44</v>
+        <v>47.13</v>
       </c>
       <c r="F31" s="2" t="n">
-        <v>45789</v>
+        <v>45788</v>
       </c>
       <c r="G31" t="n">
-        <v>0.20647936</v>
+        <v>0.22212369</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>1747094400000</v>
+        <v>1747008000000</v>
       </c>
       <c r="B32" t="n">
-        <v>44.83</v>
+        <v>47.13</v>
       </c>
       <c r="C32" t="n">
-        <v>45.96</v>
+        <v>48.45</v>
       </c>
       <c r="D32" t="n">
-        <v>44.65</v>
+        <v>45.29</v>
       </c>
       <c r="E32" t="n">
-        <v>45.71</v>
+        <v>45.44</v>
       </c>
       <c r="F32" s="2" t="n">
-        <v>45790</v>
+        <v>45789</v>
       </c>
       <c r="G32" t="n">
-        <v>0.20894041</v>
+        <v>0.20647936</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>1747180800000</v>
+        <v>1747094400000</v>
       </c>
       <c r="B33" t="n">
-        <v>45.71</v>
+        <v>44.83</v>
       </c>
       <c r="C33" t="n">
-        <v>45.76</v>
+        <v>45.96</v>
       </c>
       <c r="D33" t="n">
         <v>44.65</v>
       </c>
       <c r="E33" t="n">
-        <v>44.79</v>
+        <v>45.71</v>
       </c>
       <c r="F33" s="2" t="n">
-        <v>45791</v>
+        <v>45790</v>
       </c>
       <c r="G33" t="n">
-        <v>0.20061441</v>
+        <v>0.20894041</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>1747267200000</v>
+        <v>1747180800000</v>
       </c>
       <c r="B34" t="n">
+        <v>45.71</v>
+      </c>
+      <c r="C34" t="n">
+        <v>45.76</v>
+      </c>
+      <c r="D34" t="n">
+        <v>44.65</v>
+      </c>
+      <c r="E34" t="n">
         <v>44.79</v>
       </c>
-      <c r="C34" t="n">
-        <v>44.85</v>
-      </c>
-      <c r="D34" t="n">
-        <v>43.07</v>
-      </c>
-      <c r="E34" t="n">
-        <v>43.57</v>
-      </c>
       <c r="F34" s="2" t="n">
-        <v>45792</v>
+        <v>45791</v>
       </c>
       <c r="G34" t="n">
-        <v>0.18983449</v>
+        <v>0.20061441</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>1747353600000</v>
+        <v>1747267200000</v>
       </c>
       <c r="B35" t="n">
+        <v>44.79</v>
+      </c>
+      <c r="C35" t="n">
+        <v>44.85</v>
+      </c>
+      <c r="D35" t="n">
+        <v>43.07</v>
+      </c>
+      <c r="E35" t="n">
         <v>43.57</v>
       </c>
-      <c r="C35" t="n">
-        <v>43.61</v>
-      </c>
-      <c r="D35" t="n">
-        <v>41.56</v>
-      </c>
-      <c r="E35" t="n">
-        <v>42.62</v>
-      </c>
       <c r="F35" s="2" t="n">
-        <v>45793</v>
+        <v>45792</v>
       </c>
       <c r="G35" t="n">
-        <v>0.18164644</v>
+        <v>0.18983449</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>1747440000000</v>
+        <v>1747353600000</v>
       </c>
       <c r="B36" t="n">
+        <v>43.57</v>
+      </c>
+      <c r="C36" t="n">
+        <v>43.61</v>
+      </c>
+      <c r="D36" t="n">
+        <v>41.56</v>
+      </c>
+      <c r="E36" t="n">
         <v>42.62</v>
       </c>
-      <c r="C36" t="n">
-        <v>43.25</v>
-      </c>
-      <c r="D36" t="n">
-        <v>42.21</v>
-      </c>
-      <c r="E36" t="n">
-        <v>43.13</v>
-      </c>
       <c r="F36" s="2" t="n">
-        <v>45794</v>
+        <v>45793</v>
       </c>
       <c r="G36" t="n">
-        <v>0.18601969</v>
+        <v>0.18164644</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>1747526400000</v>
+        <v>1747440000000</v>
       </c>
       <c r="B37" t="n">
+        <v>42.62</v>
+      </c>
+      <c r="C37" t="n">
+        <v>43.25</v>
+      </c>
+      <c r="D37" t="n">
+        <v>42.21</v>
+      </c>
+      <c r="E37" t="n">
         <v>43.13</v>
       </c>
-      <c r="C37" t="n">
-        <v>45.79</v>
-      </c>
-      <c r="D37" t="n">
-        <v>43.04</v>
-      </c>
-      <c r="E37" t="n">
-        <v>44.93</v>
-      </c>
       <c r="F37" s="2" t="n">
-        <v>45795</v>
+        <v>45794</v>
       </c>
       <c r="G37" t="n">
-        <v>0.20187049</v>
+        <v>0.18601969</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>1747612800000</v>
+        <v>1747526400000</v>
       </c>
       <c r="B38" t="n">
+        <v>43.13</v>
+      </c>
+      <c r="C38" t="n">
+        <v>45.79</v>
+      </c>
+      <c r="D38" t="n">
+        <v>43.04</v>
+      </c>
+      <c r="E38" t="n">
         <v>44.93</v>
       </c>
-      <c r="C38" t="n">
-        <v>45.24</v>
-      </c>
-      <c r="D38" t="n">
-        <v>43.77</v>
-      </c>
-      <c r="E38" t="n">
-        <v>44.02</v>
-      </c>
       <c r="F38" s="2" t="n">
-        <v>45796</v>
+        <v>45795</v>
       </c>
       <c r="G38" t="n">
-        <v>0.19377604</v>
+        <v>0.20187049</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>1747699200000</v>
+        <v>1747612800000</v>
       </c>
       <c r="B39" t="n">
+        <v>44.93</v>
+      </c>
+      <c r="C39" t="n">
+        <v>45.24</v>
+      </c>
+      <c r="D39" t="n">
+        <v>43.77</v>
+      </c>
+      <c r="E39" t="n">
         <v>44.02</v>
       </c>
-      <c r="C39" t="n">
-        <v>47.38</v>
-      </c>
-      <c r="D39" t="n">
-        <v>44.01</v>
-      </c>
-      <c r="E39" t="n">
-        <v>47.3</v>
-      </c>
       <c r="F39" s="2" t="n">
-        <v>45797</v>
+        <v>45796</v>
       </c>
       <c r="G39" t="n">
-        <v>0.223729</v>
+        <v>0.19377604</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>1747785600000</v>
+        <v>1747699200000</v>
       </c>
       <c r="B40" t="n">
+        <v>44.02</v>
+      </c>
+      <c r="C40" t="n">
+        <v>47.38</v>
+      </c>
+      <c r="D40" t="n">
+        <v>44.01</v>
+      </c>
+      <c r="E40" t="n">
         <v>47.3</v>
       </c>
-      <c r="C40" t="n">
-        <v>49.24</v>
-      </c>
-      <c r="D40" t="n">
-        <v>46.31</v>
-      </c>
-      <c r="E40" t="n">
-        <v>49.13</v>
-      </c>
       <c r="F40" s="2" t="n">
-        <v>45798</v>
+        <v>45797</v>
       </c>
       <c r="G40" t="n">
-        <v>0.24137569</v>
+        <v>0.223729</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>1747872000000</v>
+        <v>1747785600000</v>
       </c>
       <c r="B41" t="n">
+        <v>47.3</v>
+      </c>
+      <c r="C41" t="n">
+        <v>49.24</v>
+      </c>
+      <c r="D41" t="n">
+        <v>46.31</v>
+      </c>
+      <c r="E41" t="n">
         <v>49.13</v>
       </c>
-      <c r="C41" t="n">
-        <v>49.84</v>
-      </c>
-      <c r="D41" t="n">
-        <v>47.71</v>
-      </c>
-      <c r="E41" t="n">
-        <v>49</v>
-      </c>
       <c r="F41" s="2" t="n">
-        <v>45799</v>
+        <v>45798</v>
       </c>
       <c r="G41" t="n">
-        <v>0.2401</v>
+        <v>0.24137569</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>1747958400000</v>
+        <v>1747872000000</v>
       </c>
       <c r="B42" t="n">
+        <v>49.13</v>
+      </c>
+      <c r="C42" t="n">
+        <v>49.84</v>
+      </c>
+      <c r="D42" t="n">
+        <v>47.71</v>
+      </c>
+      <c r="E42" t="n">
         <v>49</v>
       </c>
-      <c r="C42" t="n">
-        <v>49</v>
-      </c>
-      <c r="D42" t="n">
-        <v>45.6</v>
-      </c>
-      <c r="E42" t="n">
-        <v>47.68</v>
-      </c>
       <c r="F42" s="2" t="n">
-        <v>45800</v>
+        <v>45799</v>
       </c>
       <c r="G42" t="n">
-        <v>0.22733824</v>
+        <v>0.2401</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>1748044800000</v>
+        <v>1747958400000</v>
       </c>
       <c r="B43" t="n">
+        <v>49</v>
+      </c>
+      <c r="C43" t="n">
+        <v>49</v>
+      </c>
+      <c r="D43" t="n">
+        <v>45.6</v>
+      </c>
+      <c r="E43" t="n">
         <v>47.68</v>
       </c>
-      <c r="C43" t="n">
-        <v>48.54</v>
-      </c>
-      <c r="D43" t="n">
-        <v>46.96</v>
-      </c>
-      <c r="E43" t="n">
-        <v>47.53</v>
-      </c>
       <c r="F43" s="2" t="n">
-        <v>45801</v>
+        <v>45800</v>
       </c>
       <c r="G43" t="n">
-        <v>0.22591009</v>
+        <v>0.22733824</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>1748131200000</v>
+        <v>1748044800000</v>
       </c>
       <c r="B44" t="n">
+        <v>47.68</v>
+      </c>
+      <c r="C44" t="n">
+        <v>48.54</v>
+      </c>
+      <c r="D44" t="n">
+        <v>46.96</v>
+      </c>
+      <c r="E44" t="n">
         <v>47.53</v>
       </c>
-      <c r="C44" t="n">
-        <v>49.34</v>
-      </c>
-      <c r="D44" t="n">
-        <v>47.34</v>
-      </c>
-      <c r="E44" t="n">
-        <v>48.96</v>
-      </c>
       <c r="F44" s="2" t="n">
-        <v>45802</v>
+        <v>45801</v>
       </c>
       <c r="G44" t="n">
-        <v>0.23970816</v>
+        <v>0.22591009</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>1748217600000</v>
+        <v>1748131200000</v>
       </c>
       <c r="B45" t="n">
-        <v>48.97</v>
+        <v>47.53</v>
       </c>
       <c r="C45" t="n">
-        <v>48.97</v>
+        <v>49.34</v>
       </c>
       <c r="D45" t="n">
-        <v>46.48</v>
+        <v>47.34</v>
       </c>
       <c r="E45" t="n">
-        <v>47.13</v>
+        <v>48.96</v>
       </c>
       <c r="F45" s="2" t="n">
-        <v>45803</v>
+        <v>45802</v>
       </c>
       <c r="G45" t="n">
-        <v>0.22212369</v>
+        <v>0.23970816</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>1748304000000</v>
+        <v>1748217600000</v>
       </c>
       <c r="B46" t="n">
+        <v>48.97</v>
+      </c>
+      <c r="C46" t="n">
+        <v>48.97</v>
+      </c>
+      <c r="D46" t="n">
+        <v>46.48</v>
+      </c>
+      <c r="E46" t="n">
         <v>47.13</v>
       </c>
-      <c r="C46" t="n">
-        <v>47.43</v>
-      </c>
-      <c r="D46" t="n">
-        <v>45.3</v>
-      </c>
-      <c r="E46" t="n">
-        <v>46.16</v>
-      </c>
       <c r="F46" s="2" t="n">
-        <v>45804</v>
+        <v>45803</v>
       </c>
       <c r="G46" t="n">
-        <v>0.21307456</v>
+        <v>0.22212369</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>1748390400000</v>
+        <v>1748304000000</v>
       </c>
       <c r="B47" t="n">
+        <v>47.13</v>
+      </c>
+      <c r="C47" t="n">
+        <v>47.43</v>
+      </c>
+      <c r="D47" t="n">
+        <v>45.3</v>
+      </c>
+      <c r="E47" t="n">
         <v>46.16</v>
       </c>
-      <c r="C47" t="n">
-        <v>46.46</v>
-      </c>
-      <c r="D47" t="n">
-        <v>43.47</v>
-      </c>
-      <c r="E47" t="n">
-        <v>45.24</v>
-      </c>
       <c r="F47" s="2" t="n">
-        <v>45805</v>
+        <v>45804</v>
       </c>
       <c r="G47" t="n">
-        <v>0.20466576</v>
+        <v>0.21307456</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>1748476800000</v>
+        <v>1748390400000</v>
       </c>
       <c r="B48" t="n">
+        <v>46.16</v>
+      </c>
+      <c r="C48" t="n">
+        <v>46.46</v>
+      </c>
+      <c r="D48" t="n">
+        <v>43.47</v>
+      </c>
+      <c r="E48" t="n">
         <v>45.24</v>
       </c>
-      <c r="C48" t="n">
-        <v>45.24</v>
-      </c>
-      <c r="D48" t="n">
-        <v>43.54</v>
-      </c>
-      <c r="E48" t="n">
-        <v>44.61</v>
-      </c>
       <c r="F48" s="2" t="n">
-        <v>45806</v>
+        <v>45805</v>
       </c>
       <c r="G48" t="n">
-        <v>0.19900521</v>
+        <v>0.20466576</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>1748563200000</v>
+        <v>1748476800000</v>
       </c>
       <c r="B49" t="n">
+        <v>45.24</v>
+      </c>
+      <c r="C49" t="n">
+        <v>45.24</v>
+      </c>
+      <c r="D49" t="n">
+        <v>43.54</v>
+      </c>
+      <c r="E49" t="n">
         <v>44.61</v>
       </c>
-      <c r="C49" t="n">
-        <v>47.41</v>
-      </c>
-      <c r="D49" t="n">
-        <v>43.64</v>
-      </c>
-      <c r="E49" t="n">
-        <v>43.71</v>
-      </c>
       <c r="F49" s="2" t="n">
-        <v>45807</v>
+        <v>45806</v>
       </c>
       <c r="G49" t="n">
-        <v>0.19105641</v>
+        <v>0.19900521</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>1748649600000</v>
+        <v>1748563200000</v>
       </c>
       <c r="B50" t="n">
-        <v>43.72</v>
+        <v>44.61</v>
       </c>
       <c r="C50" t="n">
-        <v>46.61</v>
+        <v>47.41</v>
       </c>
       <c r="D50" t="n">
-        <v>42.94</v>
+        <v>43.64</v>
       </c>
       <c r="E50" t="n">
-        <v>45.88</v>
+        <v>43.71</v>
       </c>
       <c r="F50" s="2" t="n">
-        <v>45808</v>
+        <v>45807</v>
       </c>
       <c r="G50" t="n">
-        <v>0.21049744</v>
+        <v>0.19105641</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>1748736000000</v>
+        <v>1748649600000</v>
       </c>
       <c r="B51" t="n">
+        <v>43.72</v>
+      </c>
+      <c r="C51" t="n">
+        <v>46.61</v>
+      </c>
+      <c r="D51" t="n">
+        <v>42.94</v>
+      </c>
+      <c r="E51" t="n">
         <v>45.88</v>
       </c>
-      <c r="C51" t="n">
-        <v>46.68</v>
-      </c>
-      <c r="D51" t="n">
-        <v>45.08</v>
-      </c>
-      <c r="E51" t="n">
-        <v>45.13</v>
-      </c>
       <c r="F51" s="2" t="n">
-        <v>45809</v>
+        <v>45808</v>
       </c>
       <c r="G51" t="n">
-        <v>0.20367169</v>
+        <v>0.21049744</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>1748822400000</v>
+        <v>1748736000000</v>
       </c>
       <c r="B52" t="n">
+        <v>45.88</v>
+      </c>
+      <c r="C52" t="n">
+        <v>46.68</v>
+      </c>
+      <c r="D52" t="n">
+        <v>45.08</v>
+      </c>
+      <c r="E52" t="n">
         <v>45.13</v>
       </c>
-      <c r="C52" t="n">
-        <v>45.22</v>
-      </c>
-      <c r="D52" t="n">
-        <v>42.38</v>
-      </c>
-      <c r="E52" t="n">
-        <v>42.97</v>
-      </c>
       <c r="F52" s="2" t="n">
-        <v>45810</v>
+        <v>45809</v>
       </c>
       <c r="G52" t="n">
-        <v>0.18464209</v>
+        <v>0.20367169</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>1748908800000</v>
+        <v>1748822400000</v>
       </c>
       <c r="B53" t="n">
+        <v>45.13</v>
+      </c>
+      <c r="C53" t="n">
+        <v>45.22</v>
+      </c>
+      <c r="D53" t="n">
+        <v>42.38</v>
+      </c>
+      <c r="E53" t="n">
         <v>42.97</v>
       </c>
-      <c r="C53" t="n">
-        <v>43.72</v>
-      </c>
-      <c r="D53" t="n">
-        <v>42.47</v>
-      </c>
-      <c r="E53" t="n">
-        <v>42.83</v>
-      </c>
       <c r="F53" s="2" t="n">
-        <v>45811</v>
+        <v>45810</v>
       </c>
       <c r="G53" t="n">
-        <v>0.18344089</v>
+        <v>0.18464209</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>1748995200000</v>
+        <v>1748908800000</v>
       </c>
       <c r="B54" t="n">
+        <v>42.97</v>
+      </c>
+      <c r="C54" t="n">
+        <v>43.72</v>
+      </c>
+      <c r="D54" t="n">
+        <v>42.47</v>
+      </c>
+      <c r="E54" t="n">
         <v>42.83</v>
       </c>
-      <c r="C54" t="n">
-        <v>43.08</v>
-      </c>
-      <c r="D54" t="n">
-        <v>41.83</v>
-      </c>
-      <c r="E54" t="n">
-        <v>42.18</v>
-      </c>
       <c r="F54" s="2" t="n">
-        <v>45812</v>
+        <v>45811</v>
       </c>
       <c r="G54" t="n">
-        <v>0.17791524</v>
+        <v>0.18344089</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>1749081600000</v>
+        <v>1748995200000</v>
       </c>
       <c r="B55" t="n">
+        <v>42.83</v>
+      </c>
+      <c r="C55" t="n">
+        <v>43.08</v>
+      </c>
+      <c r="D55" t="n">
+        <v>41.83</v>
+      </c>
+      <c r="E55" t="n">
         <v>42.18</v>
       </c>
-      <c r="C55" t="n">
-        <v>43.45</v>
-      </c>
-      <c r="D55" t="n">
-        <v>41.44</v>
-      </c>
-      <c r="E55" t="n">
-        <v>42.76</v>
-      </c>
       <c r="F55" s="2" t="n">
-        <v>45813</v>
+        <v>45812</v>
       </c>
       <c r="G55" t="n">
-        <v>0.18284176</v>
+        <v>0.17791524</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>1749168000000</v>
+        <v>1749081600000</v>
       </c>
       <c r="B56" t="n">
+        <v>42.18</v>
+      </c>
+      <c r="C56" t="n">
+        <v>43.45</v>
+      </c>
+      <c r="D56" t="n">
+        <v>41.44</v>
+      </c>
+      <c r="E56" t="n">
         <v>42.76</v>
       </c>
-      <c r="C56" t="n">
-        <v>42.89</v>
-      </c>
-      <c r="D56" t="n">
-        <v>40.52</v>
-      </c>
-      <c r="E56" t="n">
-        <v>40.53</v>
-      </c>
       <c r="F56" s="2" t="n">
-        <v>45814</v>
+        <v>45813</v>
       </c>
       <c r="G56" t="n">
-        <v>0.16426809</v>
+        <v>0.18284176</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>1749254400000</v>
+        <v>1749168000000</v>
       </c>
       <c r="B57" t="n">
+        <v>42.76</v>
+      </c>
+      <c r="C57" t="n">
+        <v>42.89</v>
+      </c>
+      <c r="D57" t="n">
+        <v>40.52</v>
+      </c>
+      <c r="E57" t="n">
         <v>40.53</v>
       </c>
-      <c r="C57" t="n">
-        <v>42.12</v>
-      </c>
-      <c r="D57" t="n">
-        <v>40.53</v>
-      </c>
-      <c r="E57" t="n">
-        <v>41.99</v>
-      </c>
       <c r="F57" s="2" t="n">
-        <v>45815</v>
+        <v>45814</v>
       </c>
       <c r="G57" t="n">
-        <v>0.17631601</v>
+        <v>0.16426809</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>1749340800000</v>
+        <v>1749254400000</v>
       </c>
       <c r="B58" t="n">
+        <v>40.53</v>
+      </c>
+      <c r="C58" t="n">
+        <v>42.12</v>
+      </c>
+      <c r="D58" t="n">
+        <v>40.53</v>
+      </c>
+      <c r="E58" t="n">
         <v>41.99</v>
       </c>
-      <c r="C58" t="n">
-        <v>42.64</v>
-      </c>
-      <c r="D58" t="n">
-        <v>41.54</v>
-      </c>
-      <c r="E58" t="n">
-        <v>42.52</v>
-      </c>
       <c r="F58" s="2" t="n">
-        <v>45816</v>
+        <v>45815</v>
       </c>
       <c r="G58" t="n">
-        <v>0.18079504</v>
+        <v>0.17631601</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>1749427200000</v>
+        <v>1749340800000</v>
       </c>
       <c r="B59" t="n">
+        <v>41.99</v>
+      </c>
+      <c r="C59" t="n">
+        <v>42.64</v>
+      </c>
+      <c r="D59" t="n">
+        <v>41.54</v>
+      </c>
+      <c r="E59" t="n">
         <v>42.52</v>
       </c>
-      <c r="C59" t="n">
-        <v>42.85</v>
-      </c>
-      <c r="D59" t="n">
-        <v>41.46</v>
-      </c>
-      <c r="E59" t="n">
-        <v>42.61</v>
-      </c>
       <c r="F59" s="2" t="n">
-        <v>45817</v>
+        <v>45816</v>
       </c>
       <c r="G59" t="n">
-        <v>0.18156121</v>
+        <v>0.18079504</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>1749513600000</v>
+        <v>1749427200000</v>
       </c>
       <c r="B60" t="n">
-        <v>41.89</v>
+        <v>42.52</v>
       </c>
       <c r="C60" t="n">
-        <v>42.8</v>
+        <v>42.85</v>
       </c>
       <c r="D60" t="n">
-        <v>41.65</v>
+        <v>41.46</v>
       </c>
       <c r="E60" t="n">
-        <v>42.51</v>
+        <v>42.61</v>
       </c>
       <c r="F60" s="2" t="n">
-        <v>45818</v>
+        <v>45817</v>
       </c>
       <c r="G60" t="n">
-        <v>0.18071001</v>
+        <v>0.18156121</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>1749600000000</v>
+        <v>1749513600000</v>
       </c>
       <c r="B61" t="n">
+        <v>41.89</v>
+      </c>
+      <c r="C61" t="n">
+        <v>42.8</v>
+      </c>
+      <c r="D61" t="n">
+        <v>41.65</v>
+      </c>
+      <c r="E61" t="n">
         <v>42.51</v>
       </c>
-      <c r="C61" t="n">
-        <v>42.69</v>
-      </c>
-      <c r="D61" t="n">
-        <v>40.86</v>
-      </c>
-      <c r="E61" t="n">
-        <v>40.95</v>
-      </c>
       <c r="F61" s="2" t="n">
-        <v>45819</v>
+        <v>45818</v>
       </c>
       <c r="G61" t="n">
-        <v>0.16769025</v>
+        <v>0.18071001</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>1749686400000</v>
+        <v>1749600000000</v>
       </c>
       <c r="B62" t="n">
+        <v>42.51</v>
+      </c>
+      <c r="C62" t="n">
+        <v>42.69</v>
+      </c>
+      <c r="D62" t="n">
+        <v>40.86</v>
+      </c>
+      <c r="E62" t="n">
         <v>40.95</v>
       </c>
-      <c r="C62" t="n">
-        <v>41.4</v>
-      </c>
-      <c r="D62" t="n">
-        <v>39.57</v>
-      </c>
-      <c r="E62" t="n">
-        <v>39.77</v>
-      </c>
       <c r="F62" s="2" t="n">
-        <v>45820</v>
+        <v>45819</v>
       </c>
       <c r="G62" t="n">
-        <v>0.15816529</v>
+        <v>0.16769025</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>1749772800000</v>
+        <v>1749686400000</v>
       </c>
       <c r="B63" t="n">
+        <v>40.95</v>
+      </c>
+      <c r="C63" t="n">
+        <v>41.4</v>
+      </c>
+      <c r="D63" t="n">
+        <v>39.57</v>
+      </c>
+      <c r="E63" t="n">
         <v>39.77</v>
       </c>
-      <c r="C63" t="n">
-        <v>43.96</v>
-      </c>
-      <c r="D63" t="n">
-        <v>39.77</v>
-      </c>
-      <c r="E63" t="n">
-        <v>40.72</v>
-      </c>
       <c r="F63" s="2" t="n">
-        <v>45821</v>
+        <v>45820</v>
       </c>
       <c r="G63" t="n">
-        <v>0.16581184</v>
+        <v>0.15816529</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>1749859200000</v>
+        <v>1749772800000</v>
       </c>
       <c r="B64" t="n">
+        <v>39.77</v>
+      </c>
+      <c r="C64" t="n">
+        <v>43.96</v>
+      </c>
+      <c r="D64" t="n">
+        <v>39.77</v>
+      </c>
+      <c r="E64" t="n">
         <v>40.72</v>
       </c>
-      <c r="C64" t="n">
-        <v>41.31</v>
-      </c>
-      <c r="D64" t="n">
-        <v>40.46</v>
-      </c>
-      <c r="E64" t="n">
-        <v>41</v>
-      </c>
       <c r="F64" s="2" t="n">
-        <v>45822</v>
+        <v>45821</v>
       </c>
       <c r="G64" t="n">
-        <v>0.1681</v>
+        <v>0.16581184</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>1749945600000</v>
+        <v>1749859200000</v>
       </c>
       <c r="B65" t="n">
+        <v>40.72</v>
+      </c>
+      <c r="C65" t="n">
+        <v>41.31</v>
+      </c>
+      <c r="D65" t="n">
+        <v>40.46</v>
+      </c>
+      <c r="E65" t="n">
         <v>41</v>
       </c>
-      <c r="C65" t="n">
-        <v>42.79</v>
-      </c>
-      <c r="D65" t="n">
-        <v>40.91</v>
-      </c>
-      <c r="E65" t="n">
-        <v>42.32</v>
-      </c>
       <c r="F65" s="2" t="n">
-        <v>45823</v>
+        <v>45822</v>
       </c>
       <c r="G65" t="n">
-        <v>0.17909824</v>
+        <v>0.1681</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>1750032000000</v>
+        <v>1749945600000</v>
       </c>
       <c r="B66" t="n">
+        <v>41</v>
+      </c>
+      <c r="C66" t="n">
+        <v>42.79</v>
+      </c>
+      <c r="D66" t="n">
+        <v>40.91</v>
+      </c>
+      <c r="E66" t="n">
         <v>42.32</v>
       </c>
-      <c r="C66" t="n">
-        <v>42.32</v>
-      </c>
-      <c r="D66" t="n">
-        <v>40.28</v>
-      </c>
-      <c r="E66" t="n">
-        <v>41.73</v>
-      </c>
       <c r="F66" s="2" t="n">
-        <v>45824</v>
+        <v>45823</v>
       </c>
       <c r="G66" t="n">
-        <v>0.1741392899999999</v>
+        <v>0.17909824</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>1750118400000</v>
+        <v>1750032000000</v>
       </c>
       <c r="B67" t="n">
+        <v>42.32</v>
+      </c>
+      <c r="C67" t="n">
+        <v>42.32</v>
+      </c>
+      <c r="D67" t="n">
+        <v>40.28</v>
+      </c>
+      <c r="E67" t="n">
         <v>41.73</v>
       </c>
-      <c r="C67" t="n">
-        <v>42.19</v>
-      </c>
-      <c r="D67" t="n">
-        <v>40.72</v>
-      </c>
-      <c r="E67" t="n">
-        <v>41.62</v>
-      </c>
       <c r="F67" s="2" t="n">
-        <v>45825</v>
+        <v>45824</v>
       </c>
       <c r="G67" t="n">
-        <v>0.17322244</v>
+        <v>0.1741392899999999</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>1750204800000</v>
+        <v>1750118400000</v>
       </c>
       <c r="B68" t="n">
+        <v>41.73</v>
+      </c>
+      <c r="C68" t="n">
+        <v>42.19</v>
+      </c>
+      <c r="D68" t="n">
+        <v>40.72</v>
+      </c>
+      <c r="E68" t="n">
         <v>41.62</v>
       </c>
-      <c r="C68" t="n">
-        <v>41.7</v>
-      </c>
-      <c r="D68" t="n">
-        <v>39.6</v>
-      </c>
-      <c r="E68" t="n">
-        <v>39.69</v>
-      </c>
       <c r="F68" s="2" t="n">
-        <v>45826</v>
+        <v>45825</v>
       </c>
       <c r="G68" t="n">
-        <v>0.15752961</v>
+        <v>0.17322244</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>1750291200000</v>
+        <v>1750204800000</v>
       </c>
       <c r="B69" t="n">
+        <v>41.62</v>
+      </c>
+      <c r="C69" t="n">
+        <v>41.7</v>
+      </c>
+      <c r="D69" t="n">
+        <v>39.6</v>
+      </c>
+      <c r="E69" t="n">
         <v>39.69</v>
       </c>
-      <c r="C69" t="n">
-        <v>40.64</v>
-      </c>
-      <c r="D69" t="n">
-        <v>39.65</v>
-      </c>
-      <c r="E69" t="n">
-        <v>40.21</v>
-      </c>
       <c r="F69" s="2" t="n">
-        <v>45827</v>
+        <v>45826</v>
       </c>
       <c r="G69" t="n">
-        <v>0.16168441</v>
+        <v>0.15752961</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>1750377600000</v>
+        <v>1750291200000</v>
       </c>
       <c r="B70" t="n">
+        <v>39.69</v>
+      </c>
+      <c r="C70" t="n">
+        <v>40.64</v>
+      </c>
+      <c r="D70" t="n">
+        <v>39.65</v>
+      </c>
+      <c r="E70" t="n">
         <v>40.21</v>
       </c>
-      <c r="C70" t="n">
-        <v>41.53</v>
-      </c>
-      <c r="D70" t="n">
-        <v>39.03</v>
-      </c>
-      <c r="E70" t="n">
-        <v>40.67</v>
-      </c>
       <c r="F70" s="2" t="n">
-        <v>45828</v>
+        <v>45827</v>
       </c>
       <c r="G70" t="n">
-        <v>0.16540489</v>
+        <v>0.16168441</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>1750464000000</v>
+        <v>1750377600000</v>
       </c>
       <c r="B71" t="n">
+        <v>40.21</v>
+      </c>
+      <c r="C71" t="n">
+        <v>41.53</v>
+      </c>
+      <c r="D71" t="n">
+        <v>39.03</v>
+      </c>
+      <c r="E71" t="n">
         <v>40.67</v>
       </c>
-      <c r="C71" t="n">
-        <v>41.43</v>
-      </c>
-      <c r="D71" t="n">
-        <v>38.9</v>
-      </c>
-      <c r="E71" t="n">
-        <v>41.01</v>
-      </c>
       <c r="F71" s="2" t="n">
-        <v>45829</v>
+        <v>45828</v>
       </c>
       <c r="G71" t="n">
-        <v>0.16818201</v>
+        <v>0.16540489</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>1750550400000</v>
+        <v>1750464000000</v>
       </c>
       <c r="B72" t="n">
+        <v>40.67</v>
+      </c>
+      <c r="C72" t="n">
+        <v>41.43</v>
+      </c>
+      <c r="D72" t="n">
+        <v>38.9</v>
+      </c>
+      <c r="E72" t="n">
         <v>41.01</v>
       </c>
-      <c r="C72" t="n">
-        <v>44.63</v>
-      </c>
-      <c r="D72" t="n">
-        <v>40.42</v>
-      </c>
-      <c r="E72" t="n">
-        <v>41.75</v>
-      </c>
       <c r="F72" s="2" t="n">
-        <v>45830</v>
+        <v>45829</v>
       </c>
       <c r="G72" t="n">
-        <v>0.17430625</v>
+        <v>0.16818201</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>1750636800000</v>
+        <v>1750550400000</v>
       </c>
       <c r="B73" t="n">
+        <v>41.01</v>
+      </c>
+      <c r="C73" t="n">
+        <v>44.63</v>
+      </c>
+      <c r="D73" t="n">
+        <v>40.42</v>
+      </c>
+      <c r="E73" t="n">
         <v>41.75</v>
       </c>
-      <c r="C73" t="n">
-        <v>42.15</v>
-      </c>
-      <c r="D73" t="n">
-        <v>39.54</v>
-      </c>
-      <c r="E73" t="n">
-        <v>39.86</v>
-      </c>
       <c r="F73" s="2" t="n">
-        <v>45831</v>
+        <v>45830</v>
       </c>
       <c r="G73" t="n">
-        <v>0.15888196</v>
+        <v>0.17430625</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>1750723200000</v>
+        <v>1750636800000</v>
       </c>
       <c r="B74" t="n">
-        <v>39.87</v>
+        <v>41.75</v>
       </c>
       <c r="C74" t="n">
-        <v>41.2</v>
+        <v>42.15</v>
       </c>
       <c r="D74" t="n">
-        <v>39</v>
+        <v>39.54</v>
       </c>
       <c r="E74" t="n">
-        <v>39.05</v>
+        <v>39.86</v>
       </c>
       <c r="F74" s="2" t="n">
-        <v>45832</v>
+        <v>45831</v>
       </c>
       <c r="G74" t="n">
-        <v>0.15249025</v>
+        <v>0.15888196</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>1750809600000</v>
+        <v>1750723200000</v>
       </c>
       <c r="B75" t="n">
-        <v>39.04</v>
+        <v>39.87</v>
       </c>
       <c r="C75" t="n">
-        <v>39.28</v>
+        <v>41.2</v>
       </c>
       <c r="D75" t="n">
-        <v>37.9</v>
+        <v>39</v>
       </c>
       <c r="E75" t="n">
-        <v>38.4</v>
+        <v>39.05</v>
       </c>
       <c r="F75" s="2" t="n">
-        <v>45833</v>
+        <v>45832</v>
       </c>
       <c r="G75" t="n">
-        <v>0.147456</v>
+        <v>0.15249025</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>1750896000000</v>
+        <v>1750809600000</v>
       </c>
       <c r="B76" t="n">
+        <v>39.04</v>
+      </c>
+      <c r="C76" t="n">
+        <v>39.28</v>
+      </c>
+      <c r="D76" t="n">
+        <v>37.9</v>
+      </c>
+      <c r="E76" t="n">
         <v>38.4</v>
       </c>
-      <c r="C76" t="n">
-        <v>39.32</v>
-      </c>
-      <c r="D76" t="n">
-        <v>37.71</v>
-      </c>
-      <c r="E76" t="n">
-        <v>38.25</v>
-      </c>
       <c r="F76" s="2" t="n">
-        <v>45834</v>
+        <v>45833</v>
       </c>
       <c r="G76" t="n">
-        <v>0.14630625</v>
+        <v>0.147456</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>1750982400000</v>
+        <v>1750896000000</v>
       </c>
       <c r="B77" t="n">
+        <v>38.4</v>
+      </c>
+      <c r="C77" t="n">
+        <v>39.32</v>
+      </c>
+      <c r="D77" t="n">
+        <v>37.71</v>
+      </c>
+      <c r="E77" t="n">
         <v>38.25</v>
       </c>
-      <c r="C77" t="n">
-        <v>38.34</v>
-      </c>
-      <c r="D77" t="n">
-        <v>36.27</v>
-      </c>
-      <c r="E77" t="n">
-        <v>38.1</v>
-      </c>
       <c r="F77" s="2" t="n">
-        <v>45835</v>
+        <v>45834</v>
       </c>
       <c r="G77" t="n">
-        <v>0.145161</v>
+        <v>0.14630625</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>1751068800000</v>
+        <v>1750982400000</v>
       </c>
       <c r="B78" t="n">
+        <v>38.25</v>
+      </c>
+      <c r="C78" t="n">
+        <v>38.34</v>
+      </c>
+      <c r="D78" t="n">
+        <v>36.27</v>
+      </c>
+      <c r="E78" t="n">
         <v>38.1</v>
       </c>
-      <c r="C78" t="n">
-        <v>38.16</v>
-      </c>
-      <c r="D78" t="n">
-        <v>36.79</v>
-      </c>
-      <c r="E78" t="n">
-        <v>37.71</v>
-      </c>
       <c r="F78" s="2" t="n">
-        <v>45836</v>
+        <v>45835</v>
       </c>
       <c r="G78" t="n">
-        <v>0.14220441</v>
+        <v>0.145161</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>1751155200000</v>
+        <v>1751068800000</v>
       </c>
       <c r="B79" t="n">
+        <v>38.1</v>
+      </c>
+      <c r="C79" t="n">
+        <v>38.16</v>
+      </c>
+      <c r="D79" t="n">
+        <v>36.79</v>
+      </c>
+      <c r="E79" t="n">
         <v>37.71</v>
       </c>
-      <c r="C79" t="n">
-        <v>39.42</v>
-      </c>
-      <c r="D79" t="n">
-        <v>37.7</v>
-      </c>
-      <c r="E79" t="n">
-        <v>39.34</v>
-      </c>
       <c r="F79" s="2" t="n">
-        <v>45837</v>
+        <v>45836</v>
       </c>
       <c r="G79" t="n">
-        <v>0.15476356</v>
+        <v>0.14220441</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>1751241600000</v>
+        <v>1751155200000</v>
       </c>
       <c r="B80" t="n">
+        <v>37.71</v>
+      </c>
+      <c r="C80" t="n">
+        <v>39.42</v>
+      </c>
+      <c r="D80" t="n">
+        <v>37.7</v>
+      </c>
+      <c r="E80" t="n">
         <v>39.34</v>
       </c>
-      <c r="C80" t="n">
-        <v>39.34</v>
-      </c>
-      <c r="D80" t="n">
-        <v>37.69</v>
-      </c>
-      <c r="E80" t="n">
-        <v>37.74</v>
-      </c>
       <c r="F80" s="2" t="n">
-        <v>45838</v>
+        <v>45837</v>
       </c>
       <c r="G80" t="n">
-        <v>0.14243076</v>
+        <v>0.15476356</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>1751328000000</v>
+        <v>1751241600000</v>
       </c>
       <c r="B81" t="n">
-        <v>37.14</v>
+        <v>39.34</v>
       </c>
       <c r="C81" t="n">
-        <v>38.23</v>
+        <v>39.34</v>
       </c>
       <c r="D81" t="n">
-        <v>36.99</v>
+        <v>37.69</v>
       </c>
       <c r="E81" t="n">
-        <v>37.61</v>
+        <v>37.74</v>
       </c>
       <c r="F81" s="2" t="n">
-        <v>45839</v>
+        <v>45838</v>
       </c>
       <c r="G81" t="n">
-        <v>0.14145121</v>
+        <v>0.14243076</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>1751414400000</v>
+        <v>1751328000000</v>
       </c>
       <c r="B82" t="n">
+        <v>37.14</v>
+      </c>
+      <c r="C82" t="n">
+        <v>38.23</v>
+      </c>
+      <c r="D82" t="n">
+        <v>36.99</v>
+      </c>
+      <c r="E82" t="n">
         <v>37.61</v>
       </c>
-      <c r="C82" t="n">
-        <v>40.44</v>
-      </c>
-      <c r="D82" t="n">
-        <v>37.48</v>
-      </c>
-      <c r="E82" t="n">
-        <v>39.6</v>
-      </c>
       <c r="F82" s="2" t="n">
-        <v>45840</v>
+        <v>45839</v>
       </c>
       <c r="G82" t="n">
-        <v>0.156816</v>
+        <v>0.14145121</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>1751500800000</v>
+        <v>1751414400000</v>
       </c>
       <c r="B83" t="n">
+        <v>37.61</v>
+      </c>
+      <c r="C83" t="n">
+        <v>40.44</v>
+      </c>
+      <c r="D83" t="n">
+        <v>37.48</v>
+      </c>
+      <c r="E83" t="n">
         <v>39.6</v>
       </c>
-      <c r="C83" t="n">
-        <v>40.93</v>
-      </c>
-      <c r="D83" t="n">
-        <v>38.66</v>
-      </c>
-      <c r="E83" t="n">
-        <v>39.08</v>
-      </c>
       <c r="F83" s="2" t="n">
-        <v>45841</v>
+        <v>45840</v>
       </c>
       <c r="G83" t="n">
-        <v>0.15272464</v>
+        <v>0.156816</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>1751587200000</v>
+        <v>1751500800000</v>
       </c>
       <c r="B84" t="n">
+        <v>39.6</v>
+      </c>
+      <c r="C84" t="n">
+        <v>40.93</v>
+      </c>
+      <c r="D84" t="n">
+        <v>38.66</v>
+      </c>
+      <c r="E84" t="n">
         <v>39.08</v>
       </c>
-      <c r="C84" t="n">
-        <v>39.63</v>
-      </c>
-      <c r="D84" t="n">
-        <v>36.79</v>
-      </c>
-      <c r="E84" t="n">
-        <v>39.21</v>
-      </c>
       <c r="F84" s="2" t="n">
-        <v>45842</v>
+        <v>45841</v>
       </c>
       <c r="G84" t="n">
-        <v>0.15374241</v>
+        <v>0.15272464</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>1751673600000</v>
+        <v>1751587200000</v>
       </c>
       <c r="B85" t="n">
+        <v>39.08</v>
+      </c>
+      <c r="C85" t="n">
+        <v>39.63</v>
+      </c>
+      <c r="D85" t="n">
+        <v>36.79</v>
+      </c>
+      <c r="E85" t="n">
         <v>39.21</v>
       </c>
-      <c r="C85" t="n">
-        <v>39.21</v>
-      </c>
-      <c r="D85" t="n">
-        <v>38.47</v>
-      </c>
-      <c r="E85" t="n">
-        <v>38.54</v>
-      </c>
       <c r="F85" s="2" t="n">
-        <v>45843</v>
+        <v>45842</v>
       </c>
       <c r="G85" t="n">
-        <v>0.14853316</v>
+        <v>0.15374241</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>1751760000000</v>
+        <v>1751673600000</v>
       </c>
       <c r="B86" t="n">
+        <v>39.21</v>
+      </c>
+      <c r="C86" t="n">
+        <v>39.21</v>
+      </c>
+      <c r="D86" t="n">
+        <v>38.47</v>
+      </c>
+      <c r="E86" t="n">
         <v>38.54</v>
       </c>
-      <c r="C86" t="n">
-        <v>39</v>
-      </c>
-      <c r="D86" t="n">
-        <v>38.24</v>
-      </c>
-      <c r="E86" t="n">
-        <v>38.98</v>
-      </c>
       <c r="F86" s="2" t="n">
-        <v>45844</v>
+        <v>45843</v>
       </c>
       <c r="G86" t="n">
-        <v>0.15194404</v>
+        <v>0.14853316</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>1751846400000</v>
+        <v>1751760000000</v>
       </c>
       <c r="B87" t="n">
+        <v>38.54</v>
+      </c>
+      <c r="C87" t="n">
+        <v>39</v>
+      </c>
+      <c r="D87" t="n">
+        <v>38.24</v>
+      </c>
+      <c r="E87" t="n">
         <v>38.98</v>
       </c>
-      <c r="C87" t="n">
-        <v>39.51</v>
-      </c>
-      <c r="D87" t="n">
-        <v>38.46</v>
-      </c>
-      <c r="E87" t="n">
-        <v>38.71</v>
-      </c>
       <c r="F87" s="2" t="n">
-        <v>45845</v>
+        <v>45844</v>
       </c>
       <c r="G87" t="n">
-        <v>0.14984641</v>
+        <v>0.15194404</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>1751932800000</v>
+        <v>1751846400000</v>
       </c>
       <c r="B88" t="n">
+        <v>38.98</v>
+      </c>
+      <c r="C88" t="n">
+        <v>39.51</v>
+      </c>
+      <c r="D88" t="n">
+        <v>38.46</v>
+      </c>
+      <c r="E88" t="n">
         <v>38.71</v>
       </c>
-      <c r="C88" t="n">
-        <v>39.04</v>
-      </c>
-      <c r="D88" t="n">
-        <v>37.67</v>
-      </c>
-      <c r="E88" t="n">
-        <v>37.77</v>
-      </c>
       <c r="F88" s="2" t="n">
-        <v>45846</v>
+        <v>45845</v>
       </c>
       <c r="G88" t="n">
-        <v>0.14265729</v>
+        <v>0.14984641</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>1752019200000</v>
+        <v>1751932800000</v>
       </c>
       <c r="B89" t="n">
+        <v>38.71</v>
+      </c>
+      <c r="C89" t="n">
+        <v>39.04</v>
+      </c>
+      <c r="D89" t="n">
+        <v>37.67</v>
+      </c>
+      <c r="E89" t="n">
         <v>37.77</v>
       </c>
-      <c r="C89" t="n">
-        <v>40.09</v>
-      </c>
-      <c r="D89" t="n">
-        <v>37.08</v>
-      </c>
-      <c r="E89" t="n">
-        <v>38.77</v>
-      </c>
       <c r="F89" s="2" t="n">
-        <v>45847</v>
+        <v>45846</v>
       </c>
       <c r="G89" t="n">
-        <v>0.15031129</v>
+        <v>0.14265729</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>1752105600000</v>
+        <v>1752019200000</v>
       </c>
       <c r="B90" t="n">
+        <v>37.77</v>
+      </c>
+      <c r="C90" t="n">
+        <v>40.09</v>
+      </c>
+      <c r="D90" t="n">
+        <v>37.08</v>
+      </c>
+      <c r="E90" t="n">
         <v>38.77</v>
       </c>
-      <c r="C90" t="n">
-        <v>40.21</v>
-      </c>
-      <c r="D90" t="n">
-        <v>37.98</v>
-      </c>
-      <c r="E90" t="n">
-        <v>38.62</v>
-      </c>
       <c r="F90" s="2" t="n">
-        <v>45848</v>
+        <v>45847</v>
       </c>
       <c r="G90" t="n">
-        <v>0.14915044</v>
+        <v>0.15031129</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>1752192000000</v>
+        <v>1752105600000</v>
       </c>
       <c r="B91" t="n">
+        <v>38.77</v>
+      </c>
+      <c r="C91" t="n">
+        <v>40.21</v>
+      </c>
+      <c r="D91" t="n">
+        <v>37.98</v>
+      </c>
+      <c r="E91" t="n">
         <v>38.62</v>
       </c>
-      <c r="C91" t="n">
-        <v>40.24</v>
-      </c>
-      <c r="D91" t="n">
-        <v>37.51</v>
-      </c>
-      <c r="E91" t="n">
-        <v>37.94</v>
-      </c>
       <c r="F91" s="2" t="n">
-        <v>45849</v>
+        <v>45848</v>
       </c>
       <c r="G91" t="n">
-        <v>0.14394436</v>
+        <v>0.14915044</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>1752278400000</v>
+        <v>1752192000000</v>
       </c>
       <c r="B92" t="n">
+        <v>38.62</v>
+      </c>
+      <c r="C92" t="n">
+        <v>40.24</v>
+      </c>
+      <c r="D92" t="n">
+        <v>37.51</v>
+      </c>
+      <c r="E92" t="n">
         <v>37.94</v>
       </c>
-      <c r="C92" t="n">
-        <v>38.43</v>
-      </c>
-      <c r="D92" t="n">
-        <v>37.18</v>
-      </c>
-      <c r="E92" t="n">
-        <v>38.2</v>
-      </c>
       <c r="F92" s="2" t="n">
-        <v>45850</v>
+        <v>45849</v>
       </c>
       <c r="G92" t="n">
-        <v>0.145924</v>
+        <v>0.14394436</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>1752364800000</v>
+        <v>1752278400000</v>
       </c>
       <c r="B93" t="n">
+        <v>37.94</v>
+      </c>
+      <c r="C93" t="n">
+        <v>38.43</v>
+      </c>
+      <c r="D93" t="n">
+        <v>37.18</v>
+      </c>
+      <c r="E93" t="n">
         <v>38.2</v>
       </c>
-      <c r="C93" t="n">
-        <v>40.62</v>
-      </c>
-      <c r="D93" t="n">
-        <v>38.18</v>
-      </c>
-      <c r="E93" t="n">
-        <v>39.24</v>
-      </c>
       <c r="F93" s="2" t="n">
-        <v>45851</v>
+        <v>45850</v>
       </c>
       <c r="G93" t="n">
-        <v>0.15397776</v>
+        <v>0.145924</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>1752451200000</v>
+        <v>1752364800000</v>
       </c>
       <c r="B94" t="n">
+        <v>38.2</v>
+      </c>
+      <c r="C94" t="n">
+        <v>40.62</v>
+      </c>
+      <c r="D94" t="n">
+        <v>38.18</v>
+      </c>
+      <c r="E94" t="n">
         <v>39.24</v>
       </c>
-      <c r="C94" t="n">
-        <v>40.64</v>
-      </c>
-      <c r="D94" t="n">
-        <v>38.79</v>
-      </c>
-      <c r="E94" t="n">
-        <v>39.64</v>
-      </c>
       <c r="F94" s="2" t="n">
-        <v>45852</v>
+        <v>45851</v>
       </c>
       <c r="G94" t="n">
-        <v>0.15713296</v>
+        <v>0.15397776</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>1752537600000</v>
+        <v>1752451200000</v>
       </c>
       <c r="B95" t="n">
+        <v>39.24</v>
+      </c>
+      <c r="C95" t="n">
+        <v>40.64</v>
+      </c>
+      <c r="D95" t="n">
+        <v>38.79</v>
+      </c>
+      <c r="E95" t="n">
         <v>39.64</v>
       </c>
-      <c r="C95" t="n">
-        <v>41.81</v>
-      </c>
-      <c r="D95" t="n">
-        <v>39.44</v>
-      </c>
-      <c r="E95" t="n">
-        <v>39.93</v>
-      </c>
       <c r="F95" s="2" t="n">
-        <v>45853</v>
+        <v>45852</v>
       </c>
       <c r="G95" t="n">
-        <v>0.15944049</v>
+        <v>0.15713296</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>1752624000000</v>
+        <v>1752537600000</v>
       </c>
       <c r="B96" t="n">
+        <v>39.64</v>
+      </c>
+      <c r="C96" t="n">
+        <v>41.81</v>
+      </c>
+      <c r="D96" t="n">
+        <v>39.44</v>
+      </c>
+      <c r="E96" t="n">
         <v>39.93</v>
       </c>
-      <c r="C96" t="n">
-        <v>40.96</v>
-      </c>
-      <c r="D96" t="n">
-        <v>37.98</v>
-      </c>
-      <c r="E96" t="n">
-        <v>39.07</v>
-      </c>
       <c r="F96" s="2" t="n">
-        <v>45854</v>
+        <v>45853</v>
       </c>
       <c r="G96" t="n">
-        <v>0.15264649</v>
+        <v>0.15944049</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>1752710400000</v>
+        <v>1752624000000</v>
       </c>
       <c r="B97" t="n">
+        <v>39.93</v>
+      </c>
+      <c r="C97" t="n">
+        <v>40.96</v>
+      </c>
+      <c r="D97" t="n">
+        <v>37.98</v>
+      </c>
+      <c r="E97" t="n">
         <v>39.07</v>
       </c>
-      <c r="C97" t="n">
-        <v>40.89</v>
-      </c>
-      <c r="D97" t="n">
-        <v>38.28</v>
-      </c>
-      <c r="E97" t="n">
-        <v>39.47</v>
-      </c>
       <c r="F97" s="2" t="n">
-        <v>45855</v>
+        <v>45854</v>
       </c>
       <c r="G97" t="n">
-        <v>0.15578809</v>
+        <v>0.15264649</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>1752796800000</v>
+        <v>1752710400000</v>
       </c>
       <c r="B98" t="n">
+        <v>39.07</v>
+      </c>
+      <c r="C98" t="n">
+        <v>40.89</v>
+      </c>
+      <c r="D98" t="n">
+        <v>38.28</v>
+      </c>
+      <c r="E98" t="n">
         <v>39.47</v>
       </c>
-      <c r="C98" t="n">
-        <v>40.7</v>
-      </c>
-      <c r="D98" t="n">
-        <v>37.63</v>
-      </c>
-      <c r="E98" t="n">
-        <v>38.6</v>
-      </c>
       <c r="F98" s="2" t="n">
-        <v>45856</v>
+        <v>45855</v>
       </c>
       <c r="G98" t="n">
-        <v>0.148996</v>
+        <v>0.15578809</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>1752883200000</v>
+        <v>1752796800000</v>
       </c>
       <c r="B99" t="n">
+        <v>39.47</v>
+      </c>
+      <c r="C99" t="n">
+        <v>40.7</v>
+      </c>
+      <c r="D99" t="n">
+        <v>37.63</v>
+      </c>
+      <c r="E99" t="n">
         <v>38.6</v>
       </c>
-      <c r="C99" t="n">
-        <v>39.01</v>
-      </c>
-      <c r="D99" t="n">
-        <v>38.13</v>
-      </c>
-      <c r="E99" t="n">
-        <v>38.85</v>
-      </c>
       <c r="F99" s="2" t="n">
-        <v>45857</v>
+        <v>45856</v>
       </c>
       <c r="G99" t="n">
-        <v>0.15093225</v>
+        <v>0.148996</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>1752969600000</v>
+        <v>1752883200000</v>
       </c>
       <c r="B100" t="n">
+        <v>38.6</v>
+      </c>
+      <c r="C100" t="n">
+        <v>39.01</v>
+      </c>
+      <c r="D100" t="n">
+        <v>38.13</v>
+      </c>
+      <c r="E100" t="n">
         <v>38.85</v>
       </c>
-      <c r="C100" t="n">
-        <v>39.89</v>
-      </c>
-      <c r="D100" t="n">
-        <v>38.63</v>
-      </c>
-      <c r="E100" t="n">
-        <v>39.23</v>
-      </c>
       <c r="F100" s="2" t="n">
-        <v>45858</v>
+        <v>45857</v>
       </c>
       <c r="G100" t="n">
-        <v>0.15389929</v>
+        <v>0.15093225</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>1753056000000</v>
+        <v>1752969600000</v>
       </c>
       <c r="B101" t="n">
+        <v>38.85</v>
+      </c>
+      <c r="C101" t="n">
+        <v>39.89</v>
+      </c>
+      <c r="D101" t="n">
+        <v>38.63</v>
+      </c>
+      <c r="E101" t="n">
         <v>39.23</v>
       </c>
-      <c r="C101" t="n">
-        <v>40.42</v>
-      </c>
-      <c r="D101" t="n">
-        <v>38.49</v>
-      </c>
-      <c r="E101" t="n">
-        <v>39.28</v>
-      </c>
       <c r="F101" s="2" t="n">
-        <v>45859</v>
+        <v>45858</v>
       </c>
       <c r="G101" t="n">
-        <v>0.15429184</v>
+        <v>0.15389929</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>1753142400000</v>
+        <v>1753056000000</v>
       </c>
       <c r="B102" t="n">
+        <v>39.23</v>
+      </c>
+      <c r="C102" t="n">
+        <v>40.42</v>
+      </c>
+      <c r="D102" t="n">
+        <v>38.49</v>
+      </c>
+      <c r="E102" t="n">
         <v>39.28</v>
       </c>
-      <c r="C102" t="n">
-        <v>39.88</v>
-      </c>
-      <c r="D102" t="n">
-        <v>38.04</v>
-      </c>
-      <c r="E102" t="n">
-        <v>39.88</v>
-      </c>
       <c r="F102" s="2" t="n">
-        <v>45860</v>
+        <v>45859</v>
       </c>
       <c r="G102" t="n">
-        <v>0.15904144</v>
+        <v>0.15429184</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>1753228800000</v>
+        <v>1753142400000</v>
       </c>
       <c r="B103" t="n">
+        <v>39.28</v>
+      </c>
+      <c r="C103" t="n">
         <v>39.88</v>
       </c>
-      <c r="C103" t="n">
-        <v>40.17</v>
-      </c>
       <c r="D103" t="n">
-        <v>38.99</v>
+        <v>38.04</v>
       </c>
       <c r="E103" t="n">
-        <v>39.58</v>
+        <v>39.88</v>
       </c>
       <c r="F103" s="2" t="n">
-        <v>45861</v>
+        <v>45860</v>
       </c>
       <c r="G103" t="n">
-        <v>0.15665764</v>
+        <v>0.15904144</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>1753315200000</v>
+        <v>1753228800000</v>
       </c>
       <c r="B104" t="n">
+        <v>39.88</v>
+      </c>
+      <c r="C104" t="n">
+        <v>40.17</v>
+      </c>
+      <c r="D104" t="n">
+        <v>38.99</v>
+      </c>
+      <c r="E104" t="n">
         <v>39.58</v>
       </c>
-      <c r="C104" t="n">
-        <v>40.85</v>
-      </c>
-      <c r="D104" t="n">
-        <v>38.61</v>
-      </c>
-      <c r="E104" t="n">
-        <v>40.22</v>
-      </c>
       <c r="F104" s="2" t="n">
-        <v>45862</v>
+        <v>45861</v>
       </c>
       <c r="G104" t="n">
-        <v>0.16176484</v>
+        <v>0.15665764</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>1753401600000</v>
+        <v>1753315200000</v>
       </c>
       <c r="B105" t="n">
+        <v>39.58</v>
+      </c>
+      <c r="C105" t="n">
+        <v>40.85</v>
+      </c>
+      <c r="D105" t="n">
+        <v>38.61</v>
+      </c>
+      <c r="E105" t="n">
         <v>40.22</v>
       </c>
-      <c r="C105" t="n">
-        <v>43.01</v>
-      </c>
-      <c r="D105" t="n">
-        <v>39.21</v>
-      </c>
-      <c r="E105" t="n">
-        <v>40.06</v>
-      </c>
       <c r="F105" s="2" t="n">
-        <v>45863</v>
+        <v>45862</v>
       </c>
       <c r="G105" t="n">
-        <v>0.16048036</v>
+        <v>0.16176484</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>1753488000000</v>
+        <v>1753401600000</v>
       </c>
       <c r="B106" t="n">
+        <v>40.22</v>
+      </c>
+      <c r="C106" t="n">
+        <v>43.01</v>
+      </c>
+      <c r="D106" t="n">
+        <v>39.21</v>
+      </c>
+      <c r="E106" t="n">
         <v>40.06</v>
       </c>
-      <c r="C106" t="n">
-        <v>40.16</v>
-      </c>
-      <c r="D106" t="n">
-        <v>38.56</v>
-      </c>
-      <c r="E106" t="n">
-        <v>38.95</v>
-      </c>
       <c r="F106" s="2" t="n">
-        <v>45864</v>
+        <v>45863</v>
       </c>
       <c r="G106" t="n">
-        <v>0.15171025</v>
+        <v>0.16048036</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>1753574400000</v>
+        <v>1753488000000</v>
       </c>
       <c r="B107" t="n">
+        <v>40.06</v>
+      </c>
+      <c r="C107" t="n">
+        <v>40.16</v>
+      </c>
+      <c r="D107" t="n">
+        <v>38.56</v>
+      </c>
+      <c r="E107" t="n">
         <v>38.95</v>
       </c>
-      <c r="C107" t="n">
-        <v>40.55</v>
-      </c>
-      <c r="D107" t="n">
-        <v>38.73</v>
-      </c>
-      <c r="E107" t="n">
-        <v>39.37</v>
-      </c>
       <c r="F107" s="2" t="n">
-        <v>45865</v>
+        <v>45864</v>
       </c>
       <c r="G107" t="n">
-        <v>0.15499969</v>
+        <v>0.15171025</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>1753660800000</v>
+        <v>1753574400000</v>
       </c>
       <c r="B108" t="n">
+        <v>38.95</v>
+      </c>
+      <c r="C108" t="n">
+        <v>40.55</v>
+      </c>
+      <c r="D108" t="n">
+        <v>38.73</v>
+      </c>
+      <c r="E108" t="n">
         <v>39.37</v>
       </c>
-      <c r="C108" t="n">
-        <v>41.05</v>
-      </c>
-      <c r="D108" t="n">
-        <v>38.21</v>
-      </c>
-      <c r="E108" t="n">
-        <v>38.27</v>
-      </c>
       <c r="F108" s="2" t="n">
-        <v>45866</v>
+        <v>45865</v>
       </c>
       <c r="G108" t="n">
-        <v>0.14645929</v>
+        <v>0.15499969</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>1753747200000</v>
+        <v>1753660800000</v>
       </c>
       <c r="B109" t="n">
+        <v>39.37</v>
+      </c>
+      <c r="C109" t="n">
+        <v>41.05</v>
+      </c>
+      <c r="D109" t="n">
+        <v>38.21</v>
+      </c>
+      <c r="E109" t="n">
         <v>38.27</v>
       </c>
-      <c r="C109" t="n">
-        <v>38.78</v>
-      </c>
-      <c r="D109" t="n">
-        <v>34.86</v>
-      </c>
-      <c r="E109" t="n">
-        <v>35.18</v>
-      </c>
       <c r="F109" s="2" t="n">
-        <v>45867</v>
+        <v>45866</v>
       </c>
       <c r="G109" t="n">
-        <v>0.12376324</v>
+        <v>0.14645929</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>1753833600000</v>
+        <v>1753747200000</v>
       </c>
       <c r="B110" t="n">
+        <v>38.27</v>
+      </c>
+      <c r="C110" t="n">
+        <v>38.78</v>
+      </c>
+      <c r="D110" t="n">
+        <v>34.86</v>
+      </c>
+      <c r="E110" t="n">
         <v>35.18</v>
       </c>
-      <c r="C110" t="n">
-        <v>37.3</v>
-      </c>
-      <c r="D110" t="n">
-        <v>35.16</v>
-      </c>
-      <c r="E110" t="n">
-        <v>36.13</v>
-      </c>
       <c r="F110" s="2" t="n">
-        <v>45868</v>
+        <v>45867</v>
       </c>
       <c r="G110" t="n">
-        <v>0.13053769</v>
+        <v>0.12376324</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>1753920000000</v>
+        <v>1753833600000</v>
       </c>
       <c r="B111" t="n">
+        <v>35.18</v>
+      </c>
+      <c r="C111" t="n">
+        <v>37.3</v>
+      </c>
+      <c r="D111" t="n">
+        <v>35.16</v>
+      </c>
+      <c r="E111" t="n">
         <v>36.13</v>
       </c>
-      <c r="C111" t="n">
-        <v>37.02</v>
-      </c>
-      <c r="D111" t="n">
-        <v>35.79</v>
-      </c>
-      <c r="E111" t="n">
-        <v>36.73</v>
-      </c>
       <c r="F111" s="2" t="n">
-        <v>45869</v>
+        <v>45868</v>
       </c>
       <c r="G111" t="n">
-        <v>0.13490929</v>
+        <v>0.13053769</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>1754006400000</v>
+        <v>1753920000000</v>
       </c>
       <c r="B112" t="n">
+        <v>36.13</v>
+      </c>
+      <c r="C112" t="n">
+        <v>37.02</v>
+      </c>
+      <c r="D112" t="n">
+        <v>35.79</v>
+      </c>
+      <c r="E112" t="n">
         <v>36.73</v>
       </c>
-      <c r="C112" t="n">
-        <v>38.74</v>
-      </c>
-      <c r="D112" t="n">
-        <v>35.61</v>
-      </c>
-      <c r="E112" t="n">
-        <v>38.42</v>
-      </c>
       <c r="F112" s="2" t="n">
-        <v>45870</v>
+        <v>45869</v>
       </c>
       <c r="G112" t="n">
-        <v>0.14760964</v>
+        <v>0.13490929</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>1754092800000</v>
+        <v>1754006400000</v>
       </c>
       <c r="B113" t="n">
+        <v>36.73</v>
+      </c>
+      <c r="C113" t="n">
+        <v>38.74</v>
+      </c>
+      <c r="D113" t="n">
+        <v>35.61</v>
+      </c>
+      <c r="E113" t="n">
         <v>38.42</v>
       </c>
-      <c r="C113" t="n">
-        <v>38.45</v>
-      </c>
-      <c r="D113" t="n">
-        <v>36.65</v>
-      </c>
-      <c r="E113" t="n">
-        <v>37.67</v>
-      </c>
       <c r="F113" s="2" t="n">
-        <v>45871</v>
+        <v>45870</v>
       </c>
       <c r="G113" t="n">
-        <v>0.14190289</v>
+        <v>0.14760964</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>1754179200000</v>
+        <v>1754092800000</v>
       </c>
       <c r="B114" t="n">
+        <v>38.42</v>
+      </c>
+      <c r="C114" t="n">
+        <v>38.45</v>
+      </c>
+      <c r="D114" t="n">
+        <v>36.65</v>
+      </c>
+      <c r="E114" t="n">
         <v>37.67</v>
       </c>
-      <c r="C114" t="n">
-        <v>38.4</v>
-      </c>
-      <c r="D114" t="n">
-        <v>37.4</v>
-      </c>
-      <c r="E114" t="n">
-        <v>38.03</v>
-      </c>
       <c r="F114" s="2" t="n">
-        <v>45872</v>
+        <v>45871</v>
       </c>
       <c r="G114" t="n">
-        <v>0.14462809</v>
+        <v>0.14190289</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>1754265600000</v>
+        <v>1754179200000</v>
       </c>
       <c r="B115" t="n">
+        <v>37.67</v>
+      </c>
+      <c r="C115" t="n">
+        <v>38.4</v>
+      </c>
+      <c r="D115" t="n">
+        <v>37.4</v>
+      </c>
+      <c r="E115" t="n">
         <v>38.03</v>
       </c>
-      <c r="C115" t="n">
-        <v>38.1</v>
-      </c>
-      <c r="D115" t="n">
-        <v>36.78</v>
-      </c>
-      <c r="E115" t="n">
-        <v>36.89</v>
-      </c>
       <c r="F115" s="2" t="n">
-        <v>45873</v>
+        <v>45872</v>
       </c>
       <c r="G115" t="n">
-        <v>0.13608721</v>
+        <v>0.14462809</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>1754352000000</v>
+        <v>1754265600000</v>
       </c>
       <c r="B116" t="n">
-        <v>36.32</v>
+        <v>38.03</v>
       </c>
       <c r="C116" t="n">
-        <v>36.58</v>
+        <v>38.1</v>
       </c>
       <c r="D116" t="n">
-        <v>35.45</v>
+        <v>36.78</v>
       </c>
       <c r="E116" t="n">
-        <v>36.01</v>
+        <v>36.89</v>
       </c>
       <c r="F116" s="2" t="n">
-        <v>45874</v>
+        <v>45873</v>
       </c>
       <c r="G116" t="n">
-        <v>0.12967201</v>
+        <v>0.13608721</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>1754438400000</v>
+        <v>1754352000000</v>
       </c>
       <c r="B117" t="n">
+        <v>36.32</v>
+      </c>
+      <c r="C117" t="n">
+        <v>36.58</v>
+      </c>
+      <c r="D117" t="n">
+        <v>35.45</v>
+      </c>
+      <c r="E117" t="n">
         <v>36.01</v>
       </c>
-      <c r="C117" t="n">
-        <v>36.11</v>
-      </c>
-      <c r="D117" t="n">
-        <v>34.87</v>
-      </c>
-      <c r="E117" t="n">
-        <v>34.88</v>
-      </c>
       <c r="F117" s="2" t="n">
-        <v>45875</v>
+        <v>45874</v>
       </c>
       <c r="G117" t="n">
-        <v>0.12166144</v>
+        <v>0.12967201</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>1754524800000</v>
+        <v>1754438400000</v>
       </c>
       <c r="B118" t="n">
+        <v>36.01</v>
+      </c>
+      <c r="C118" t="n">
+        <v>36.11</v>
+      </c>
+      <c r="D118" t="n">
+        <v>34.87</v>
+      </c>
+      <c r="E118" t="n">
         <v>34.88</v>
       </c>
-      <c r="C118" t="n">
-        <v>35.68</v>
-      </c>
-      <c r="D118" t="n">
-        <v>33.98</v>
-      </c>
-      <c r="E118" t="n">
-        <v>35.66</v>
-      </c>
       <c r="F118" s="2" t="n">
-        <v>45876</v>
+        <v>45875</v>
       </c>
       <c r="G118" t="n">
-        <v>0.12716356</v>
+        <v>0.12166144</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>1754611200000</v>
+        <v>1754524800000</v>
       </c>
       <c r="B119" t="n">
+        <v>34.88</v>
+      </c>
+      <c r="C119" t="n">
+        <v>35.68</v>
+      </c>
+      <c r="D119" t="n">
+        <v>33.98</v>
+      </c>
+      <c r="E119" t="n">
         <v>35.66</v>
       </c>
-      <c r="C119" t="n">
-        <v>35.73</v>
-      </c>
-      <c r="D119" t="n">
-        <v>33.53</v>
-      </c>
-      <c r="E119" t="n">
-        <v>34.4</v>
-      </c>
       <c r="F119" s="2" t="n">
-        <v>45877</v>
+        <v>45876</v>
       </c>
       <c r="G119" t="n">
-        <v>0.118336</v>
+        <v>0.12716356</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>1754697600000</v>
+        <v>1754611200000</v>
       </c>
       <c r="B120" t="n">
+        <v>35.66</v>
+      </c>
+      <c r="C120" t="n">
+        <v>35.73</v>
+      </c>
+      <c r="D120" t="n">
+        <v>33.53</v>
+      </c>
+      <c r="E120" t="n">
         <v>34.4</v>
       </c>
-      <c r="C120" t="n">
-        <v>35.21</v>
-      </c>
-      <c r="D120" t="n">
-        <v>33.77</v>
-      </c>
-      <c r="E120" t="n">
-        <v>35.07</v>
-      </c>
       <c r="F120" s="2" t="n">
-        <v>45878</v>
+        <v>45877</v>
       </c>
       <c r="G120" t="n">
-        <v>0.12299049</v>
+        <v>0.118336</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>1754784000000</v>
+        <v>1754697600000</v>
       </c>
       <c r="B121" t="n">
+        <v>34.4</v>
+      </c>
+      <c r="C121" t="n">
+        <v>35.21</v>
+      </c>
+      <c r="D121" t="n">
+        <v>33.77</v>
+      </c>
+      <c r="E121" t="n">
         <v>35.07</v>
       </c>
-      <c r="C121" t="n">
-        <v>36.19</v>
-      </c>
-      <c r="D121" t="n">
-        <v>34.29</v>
-      </c>
-      <c r="E121" t="n">
-        <v>35.43</v>
-      </c>
       <c r="F121" s="2" t="n">
-        <v>45879</v>
+        <v>45878</v>
       </c>
       <c r="G121" t="n">
-        <v>0.12552849</v>
+        <v>0.12299049</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>1754870400000</v>
+        <v>1754784000000</v>
       </c>
       <c r="B122" t="n">
+        <v>35.07</v>
+      </c>
+      <c r="C122" t="n">
+        <v>36.19</v>
+      </c>
+      <c r="D122" t="n">
+        <v>34.29</v>
+      </c>
+      <c r="E122" t="n">
         <v>35.43</v>
       </c>
-      <c r="C122" t="n">
-        <v>37.93</v>
-      </c>
-      <c r="D122" t="n">
-        <v>35.04</v>
-      </c>
-      <c r="E122" t="n">
-        <v>36.56</v>
-      </c>
       <c r="F122" s="2" t="n">
-        <v>45880</v>
+        <v>45879</v>
       </c>
       <c r="G122" t="n">
-        <v>0.13366336</v>
+        <v>0.12552849</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>1754956800000</v>
+        <v>1754870400000</v>
       </c>
       <c r="B123" t="n">
+        <v>35.43</v>
+      </c>
+      <c r="C123" t="n">
+        <v>37.93</v>
+      </c>
+      <c r="D123" t="n">
+        <v>35.04</v>
+      </c>
+      <c r="E123" t="n">
         <v>36.56</v>
       </c>
-      <c r="C123" t="n">
-        <v>37.09</v>
-      </c>
-      <c r="D123" t="n">
-        <v>35.33</v>
-      </c>
-      <c r="E123" t="n">
-        <v>36.94</v>
-      </c>
       <c r="F123" s="2" t="n">
-        <v>45881</v>
+        <v>45880</v>
       </c>
       <c r="G123" t="n">
-        <v>0.13645636</v>
+        <v>0.13366336</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>1755043200000</v>
+        <v>1754956800000</v>
       </c>
       <c r="B124" t="n">
-        <v>37.41</v>
+        <v>36.56</v>
       </c>
       <c r="C124" t="n">
-        <v>39.89</v>
+        <v>37.09</v>
       </c>
       <c r="D124" t="n">
-        <v>37.07</v>
+        <v>35.33</v>
       </c>
       <c r="E124" t="n">
-        <v>39</v>
+        <v>36.94</v>
       </c>
       <c r="F124" s="2" t="n">
-        <v>45882</v>
+        <v>45881</v>
       </c>
       <c r="G124" t="n">
-        <v>0.1521</v>
+        <v>0.13645636</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>1755129600000</v>
+        <v>1755043200000</v>
       </c>
       <c r="B125" t="n">
+        <v>37.41</v>
+      </c>
+      <c r="C125" t="n">
+        <v>39.89</v>
+      </c>
+      <c r="D125" t="n">
+        <v>37.07</v>
+      </c>
+      <c r="E125" t="n">
         <v>39</v>
       </c>
-      <c r="C125" t="n">
-        <v>39.63</v>
-      </c>
-      <c r="D125" t="n">
-        <v>36.25</v>
-      </c>
-      <c r="E125" t="n">
-        <v>36.95</v>
-      </c>
       <c r="F125" s="2" t="n">
-        <v>45883</v>
+        <v>45882</v>
       </c>
       <c r="G125" t="n">
-        <v>0.13653025</v>
+        <v>0.1521</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>1755216000000</v>
+        <v>1755129600000</v>
       </c>
       <c r="B126" t="n">
+        <v>39</v>
+      </c>
+      <c r="C126" t="n">
+        <v>39.63</v>
+      </c>
+      <c r="D126" t="n">
+        <v>36.25</v>
+      </c>
+      <c r="E126" t="n">
         <v>36.95</v>
       </c>
-      <c r="C126" t="n">
-        <v>37.03</v>
-      </c>
-      <c r="D126" t="n">
-        <v>35.14</v>
-      </c>
-      <c r="E126" t="n">
-        <v>35.37</v>
-      </c>
       <c r="F126" s="2" t="n">
-        <v>45884</v>
+        <v>45883</v>
       </c>
       <c r="G126" t="n">
-        <v>0.12510369</v>
+        <v>0.13653025</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>1755302400000</v>
+        <v>1755216000000</v>
       </c>
       <c r="B127" t="n">
+        <v>36.95</v>
+      </c>
+      <c r="C127" t="n">
+        <v>37.03</v>
+      </c>
+      <c r="D127" t="n">
+        <v>35.14</v>
+      </c>
+      <c r="E127" t="n">
         <v>35.37</v>
       </c>
-      <c r="C127" t="n">
-        <v>35.46</v>
-      </c>
-      <c r="D127" t="n">
-        <v>34.93</v>
-      </c>
-      <c r="E127" t="n">
-        <v>35.38</v>
-      </c>
       <c r="F127" s="2" t="n">
-        <v>45885</v>
+        <v>45884</v>
       </c>
       <c r="G127" t="n">
-        <v>0.12517444</v>
+        <v>0.12510369</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>1755388800000</v>
+        <v>1755302400000</v>
       </c>
       <c r="B128" t="n">
+        <v>35.37</v>
+      </c>
+      <c r="C128" t="n">
+        <v>35.46</v>
+      </c>
+      <c r="D128" t="n">
+        <v>34.93</v>
+      </c>
+      <c r="E128" t="n">
         <v>35.38</v>
       </c>
-      <c r="C128" t="n">
-        <v>35.85</v>
-      </c>
-      <c r="D128" t="n">
-        <v>35.07</v>
-      </c>
-      <c r="E128" t="n">
-        <v>35.83</v>
-      </c>
       <c r="F128" s="2" t="n">
-        <v>45886</v>
+        <v>45885</v>
       </c>
       <c r="G128" t="n">
-        <v>0.12837889</v>
+        <v>0.12517444</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>1755475200000</v>
+        <v>1755388800000</v>
       </c>
       <c r="B129" t="n">
+        <v>35.38</v>
+      </c>
+      <c r="C129" t="n">
+        <v>35.85</v>
+      </c>
+      <c r="D129" t="n">
+        <v>35.07</v>
+      </c>
+      <c r="E129" t="n">
         <v>35.83</v>
       </c>
-      <c r="C129" t="n">
-        <v>38.1</v>
-      </c>
-      <c r="D129" t="n">
-        <v>35.62</v>
-      </c>
-      <c r="E129" t="n">
-        <v>35.99</v>
-      </c>
       <c r="F129" s="2" t="n">
-        <v>45887</v>
+        <v>45886</v>
       </c>
       <c r="G129" t="n">
-        <v>0.12952801</v>
+        <v>0.12837889</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>1755561600000</v>
+        <v>1755475200000</v>
       </c>
       <c r="B130" t="n">
+        <v>35.83</v>
+      </c>
+      <c r="C130" t="n">
+        <v>38.1</v>
+      </c>
+      <c r="D130" t="n">
+        <v>35.62</v>
+      </c>
+      <c r="E130" t="n">
         <v>35.99</v>
       </c>
-      <c r="C130" t="n">
-        <v>38.54</v>
-      </c>
-      <c r="D130" t="n">
-        <v>35.6</v>
-      </c>
-      <c r="E130" t="n">
-        <v>37.87</v>
-      </c>
       <c r="F130" s="2" t="n">
-        <v>45888</v>
+        <v>45887</v>
       </c>
       <c r="G130" t="n">
-        <v>0.14341369</v>
+        <v>0.12952801</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>1755648000000</v>
+        <v>1755561600000</v>
       </c>
       <c r="B131" t="n">
+        <v>35.99</v>
+      </c>
+      <c r="C131" t="n">
+        <v>38.54</v>
+      </c>
+      <c r="D131" t="n">
+        <v>35.6</v>
+      </c>
+      <c r="E131" t="n">
         <v>37.87</v>
       </c>
-      <c r="C131" t="n">
-        <v>38.01</v>
-      </c>
-      <c r="D131" t="n">
-        <v>35.91</v>
-      </c>
-      <c r="E131" t="n">
-        <v>36.02</v>
-      </c>
       <c r="F131" s="2" t="n">
-        <v>45889</v>
+        <v>45888</v>
       </c>
       <c r="G131" t="n">
-        <v>0.12974404</v>
+        <v>0.14341369</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>1755734400000</v>
+        <v>1755648000000</v>
       </c>
       <c r="B132" t="n">
+        <v>37.87</v>
+      </c>
+      <c r="C132" t="n">
+        <v>38.01</v>
+      </c>
+      <c r="D132" t="n">
+        <v>35.91</v>
+      </c>
+      <c r="E132" t="n">
         <v>36.02</v>
       </c>
-      <c r="C132" t="n">
-        <v>37.25</v>
-      </c>
-      <c r="D132" t="n">
-        <v>35.73</v>
-      </c>
-      <c r="E132" t="n">
-        <v>37.25</v>
-      </c>
       <c r="F132" s="2" t="n">
-        <v>45890</v>
+        <v>45889</v>
       </c>
       <c r="G132" t="n">
-        <v>0.13875625</v>
+        <v>0.12974404</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>1755820800000</v>
+        <v>1755734400000</v>
       </c>
       <c r="B133" t="n">
+        <v>36.02</v>
+      </c>
+      <c r="C133" t="n">
         <v>37.25</v>
       </c>
-      <c r="C133" t="n">
-        <v>37.97</v>
-      </c>
       <c r="D133" t="n">
-        <v>33.63</v>
+        <v>35.73</v>
       </c>
       <c r="E133" t="n">
-        <v>34.53</v>
+        <v>37.25</v>
       </c>
       <c r="F133" s="2" t="n">
-        <v>45891</v>
+        <v>45890</v>
       </c>
       <c r="G133" t="n">
-        <v>0.11923209</v>
+        <v>0.13875625</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>1755907200000</v>
+        <v>1755820800000</v>
       </c>
       <c r="B134" t="n">
+        <v>37.25</v>
+      </c>
+      <c r="C134" t="n">
+        <v>37.97</v>
+      </c>
+      <c r="D134" t="n">
+        <v>33.63</v>
+      </c>
+      <c r="E134" t="n">
         <v>34.53</v>
       </c>
-      <c r="C134" t="n">
-        <v>35.13</v>
-      </c>
-      <c r="D134" t="n">
-        <v>34.36</v>
-      </c>
-      <c r="E134" t="n">
-        <v>34.97</v>
-      </c>
       <c r="F134" s="2" t="n">
-        <v>45892</v>
+        <v>45891</v>
       </c>
       <c r="G134" t="n">
-        <v>0.12229009</v>
+        <v>0.11923209</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>1755993600000</v>
+        <v>1755907200000</v>
       </c>
       <c r="B135" t="n">
+        <v>34.53</v>
+      </c>
+      <c r="C135" t="n">
+        <v>35.13</v>
+      </c>
+      <c r="D135" t="n">
+        <v>34.36</v>
+      </c>
+      <c r="E135" t="n">
         <v>34.97</v>
       </c>
-      <c r="C135" t="n">
-        <v>36.87</v>
-      </c>
-      <c r="D135" t="n">
-        <v>34.3</v>
-      </c>
-      <c r="E135" t="n">
-        <v>35.07</v>
-      </c>
       <c r="F135" s="2" t="n">
-        <v>45893</v>
+        <v>45892</v>
       </c>
       <c r="G135" t="n">
-        <v>0.12299049</v>
+        <v>0.12229009</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>1756080000000</v>
+        <v>1755993600000</v>
       </c>
       <c r="B136" t="n">
+        <v>34.97</v>
+      </c>
+      <c r="C136" t="n">
+        <v>36.87</v>
+      </c>
+      <c r="D136" t="n">
+        <v>34.3</v>
+      </c>
+      <c r="E136" t="n">
         <v>35.07</v>
       </c>
-      <c r="C136" t="n">
-        <v>38.87</v>
-      </c>
-      <c r="D136" t="n">
-        <v>34.8</v>
-      </c>
-      <c r="E136" t="n">
-        <v>37.93</v>
-      </c>
       <c r="F136" s="2" t="n">
-        <v>45894</v>
+        <v>45893</v>
       </c>
       <c r="G136" t="n">
-        <v>0.14386849</v>
+        <v>0.12299049</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>1756166400000</v>
+        <v>1756080000000</v>
       </c>
       <c r="B137" t="n">
+        <v>35.07</v>
+      </c>
+      <c r="C137" t="n">
+        <v>38.87</v>
+      </c>
+      <c r="D137" t="n">
+        <v>34.8</v>
+      </c>
+      <c r="E137" t="n">
         <v>37.93</v>
       </c>
-      <c r="C137" t="n">
-        <v>40.17</v>
-      </c>
-      <c r="D137" t="n">
-        <v>36.92</v>
-      </c>
-      <c r="E137" t="n">
-        <v>36.92</v>
-      </c>
       <c r="F137" s="2" t="n">
-        <v>45895</v>
+        <v>45894</v>
       </c>
       <c r="G137" t="n">
-        <v>0.13630864</v>
+        <v>0.14386849</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>1756252800000</v>
+        <v>1756166400000</v>
       </c>
       <c r="B138" t="n">
+        <v>37.93</v>
+      </c>
+      <c r="C138" t="n">
+        <v>40.17</v>
+      </c>
+      <c r="D138" t="n">
         <v>36.92</v>
       </c>
-      <c r="C138" t="n">
-        <v>38.52</v>
-      </c>
-      <c r="D138" t="n">
-        <v>36.69</v>
-      </c>
       <c r="E138" t="n">
-        <v>37.91</v>
+        <v>36.92</v>
       </c>
       <c r="F138" s="2" t="n">
-        <v>45896</v>
+        <v>45895</v>
       </c>
       <c r="G138" t="n">
-        <v>0.14371681</v>
+        <v>0.13630864</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>1756339200000</v>
+        <v>1756252800000</v>
       </c>
       <c r="B139" t="n">
+        <v>36.92</v>
+      </c>
+      <c r="C139" t="n">
+        <v>38.52</v>
+      </c>
+      <c r="D139" t="n">
+        <v>36.69</v>
+      </c>
+      <c r="E139" t="n">
         <v>37.91</v>
       </c>
-      <c r="C139" t="n">
-        <v>38.12</v>
-      </c>
-      <c r="D139" t="n">
-        <v>36.21</v>
-      </c>
-      <c r="E139" t="n">
-        <v>36.95</v>
-      </c>
       <c r="F139" s="2" t="n">
-        <v>45897</v>
+        <v>45896</v>
       </c>
       <c r="G139" t="n">
-        <v>0.13653025</v>
+        <v>0.14371681</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>1756425600000</v>
+        <v>1756339200000</v>
       </c>
       <c r="B140" t="n">
+        <v>37.91</v>
+      </c>
+      <c r="C140" t="n">
+        <v>38.12</v>
+      </c>
+      <c r="D140" t="n">
+        <v>36.21</v>
+      </c>
+      <c r="E140" t="n">
         <v>36.95</v>
       </c>
-      <c r="C140" t="n">
-        <v>41.7</v>
-      </c>
-      <c r="D140" t="n">
-        <v>36.91</v>
-      </c>
-      <c r="E140" t="n">
-        <v>38.98</v>
-      </c>
       <c r="F140" s="2" t="n">
-        <v>45898</v>
+        <v>45897</v>
       </c>
       <c r="G140" t="n">
-        <v>0.15194404</v>
+        <v>0.13653025</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>1756512000000</v>
+        <v>1756425600000</v>
       </c>
       <c r="B141" t="n">
+        <v>36.95</v>
+      </c>
+      <c r="C141" t="n">
+        <v>41.7</v>
+      </c>
+      <c r="D141" t="n">
+        <v>36.91</v>
+      </c>
+      <c r="E141" t="n">
         <v>38.98</v>
       </c>
-      <c r="C141" t="n">
-        <v>39.4</v>
-      </c>
-      <c r="D141" t="n">
-        <v>38.36</v>
-      </c>
-      <c r="E141" t="n">
-        <v>38.85</v>
-      </c>
       <c r="F141" s="2" t="n">
-        <v>45899</v>
+        <v>45898</v>
       </c>
       <c r="G141" t="n">
-        <v>0.15093225</v>
+        <v>0.15194404</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>1756598400000</v>
+        <v>1756512000000</v>
       </c>
       <c r="B142" t="n">
+        <v>38.98</v>
+      </c>
+      <c r="C142" t="n">
+        <v>39.4</v>
+      </c>
+      <c r="D142" t="n">
+        <v>38.36</v>
+      </c>
+      <c r="E142" t="n">
         <v>38.85</v>
       </c>
-      <c r="C142" t="n">
-        <v>40</v>
-      </c>
-      <c r="D142" t="n">
-        <v>38.19</v>
-      </c>
-      <c r="E142" t="n">
-        <v>39.62</v>
-      </c>
       <c r="F142" s="2" t="n">
-        <v>45900</v>
+        <v>45899</v>
       </c>
       <c r="G142" t="n">
-        <v>0.15697444</v>
+        <v>0.15093225</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>1756684800000</v>
+        <v>1756598400000</v>
       </c>
       <c r="B143" t="n">
+        <v>38.85</v>
+      </c>
+      <c r="C143" t="n">
+        <v>40</v>
+      </c>
+      <c r="D143" t="n">
+        <v>38.19</v>
+      </c>
+      <c r="E143" t="n">
         <v>39.62</v>
       </c>
-      <c r="C143" t="n">
-        <v>39.89</v>
-      </c>
-      <c r="D143" t="n">
-        <v>37.39</v>
-      </c>
-      <c r="E143" t="n">
-        <v>39.5</v>
-      </c>
       <c r="F143" s="2" t="n">
-        <v>45901</v>
+        <v>45900</v>
       </c>
       <c r="G143" t="n">
-        <v>0.156025</v>
+        <v>0.15697444</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>1756771200000</v>
+        <v>1756684800000</v>
       </c>
       <c r="B144" t="n">
-        <v>39.33</v>
+        <v>39.62</v>
       </c>
       <c r="C144" t="n">
-        <v>40.28</v>
+        <v>39.89</v>
       </c>
       <c r="D144" t="n">
-        <v>38.69</v>
+        <v>37.39</v>
       </c>
       <c r="E144" t="n">
-        <v>38.8</v>
+        <v>39.5</v>
       </c>
       <c r="F144" s="2" t="n">
-        <v>45902</v>
+        <v>45901</v>
       </c>
       <c r="G144" t="n">
-        <v>0.150544</v>
+        <v>0.156025</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>1756857600000</v>
+        <v>1756771200000</v>
       </c>
       <c r="B145" t="n">
+        <v>39.33</v>
+      </c>
+      <c r="C145" t="n">
+        <v>40.28</v>
+      </c>
+      <c r="D145" t="n">
+        <v>38.69</v>
+      </c>
+      <c r="E145" t="n">
         <v>38.8</v>
       </c>
-      <c r="C145" t="n">
-        <v>38.88</v>
-      </c>
-      <c r="D145" t="n">
-        <v>37.97</v>
-      </c>
-      <c r="E145" t="n">
-        <v>38.85</v>
-      </c>
       <c r="F145" s="2" t="n">
-        <v>45903</v>
+        <v>45902</v>
       </c>
       <c r="G145" t="n">
-        <v>0.15093225</v>
+        <v>0.150544</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>1756944000000</v>
+        <v>1756857600000</v>
       </c>
       <c r="B146" t="n">
+        <v>38.8</v>
+      </c>
+      <c r="C146" t="n">
+        <v>38.88</v>
+      </c>
+      <c r="D146" t="n">
+        <v>37.97</v>
+      </c>
+      <c r="E146" t="n">
         <v>38.85</v>
       </c>
-      <c r="C146" t="n">
-        <v>39.17</v>
-      </c>
-      <c r="D146" t="n">
-        <v>38.37</v>
-      </c>
-      <c r="E146" t="n">
-        <v>38.48</v>
-      </c>
       <c r="F146" s="2" t="n">
-        <v>45904</v>
+        <v>45903</v>
       </c>
       <c r="G146" t="n">
-        <v>0.14807104</v>
+        <v>0.15093225</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>1757030400000</v>
+        <v>1756944000000</v>
       </c>
       <c r="B147" t="n">
+        <v>38.85</v>
+      </c>
+      <c r="C147" t="n">
+        <v>39.17</v>
+      </c>
+      <c r="D147" t="n">
+        <v>38.37</v>
+      </c>
+      <c r="E147" t="n">
         <v>38.48</v>
       </c>
-      <c r="C147" t="n">
-        <v>38.74</v>
-      </c>
-      <c r="D147" t="n">
-        <v>36.23</v>
-      </c>
-      <c r="E147" t="n">
-        <v>37.49</v>
-      </c>
       <c r="F147" s="2" t="n">
-        <v>45905</v>
+        <v>45904</v>
       </c>
       <c r="G147" t="n">
-        <v>0.14055001</v>
+        <v>0.14807104</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>1757116800000</v>
+        <v>1757030400000</v>
       </c>
       <c r="B148" t="n">
+        <v>38.48</v>
+      </c>
+      <c r="C148" t="n">
+        <v>38.74</v>
+      </c>
+      <c r="D148" t="n">
+        <v>36.23</v>
+      </c>
+      <c r="E148" t="n">
         <v>37.49</v>
       </c>
-      <c r="C148" t="n">
-        <v>38.03</v>
-      </c>
-      <c r="D148" t="n">
-        <v>37.04</v>
-      </c>
-      <c r="E148" t="n">
-        <v>37.76</v>
-      </c>
       <c r="F148" s="2" t="n">
-        <v>45906</v>
+        <v>45905</v>
       </c>
       <c r="G148" t="n">
-        <v>0.14258176</v>
+        <v>0.14055001</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>1757203200000</v>
+        <v>1757116800000</v>
       </c>
       <c r="B149" t="n">
+        <v>37.49</v>
+      </c>
+      <c r="C149" t="n">
+        <v>38.03</v>
+      </c>
+      <c r="D149" t="n">
+        <v>37.04</v>
+      </c>
+      <c r="E149" t="n">
         <v>37.76</v>
       </c>
-      <c r="C149" t="n">
-        <v>37.9</v>
-      </c>
-      <c r="D149" t="n">
-        <v>37.43</v>
-      </c>
-      <c r="E149" t="n">
-        <v>37.9</v>
-      </c>
       <c r="F149" s="2" t="n">
-        <v>45907</v>
+        <v>45906</v>
       </c>
       <c r="G149" t="n">
-        <v>0.143641</v>
+        <v>0.14258176</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>1757289600000</v>
+        <v>1757203200000</v>
       </c>
       <c r="B150" t="n">
+        <v>37.76</v>
+      </c>
+      <c r="C150" t="n">
         <v>37.9</v>
       </c>
-      <c r="C150" t="n">
-        <v>38.17</v>
-      </c>
       <c r="D150" t="n">
-        <v>36.46</v>
+        <v>37.43</v>
       </c>
       <c r="E150" t="n">
-        <v>37.08</v>
+        <v>37.9</v>
       </c>
       <c r="F150" s="2" t="n">
-        <v>45908</v>
+        <v>45907</v>
       </c>
       <c r="G150" t="n">
-        <v>0.13749264</v>
+        <v>0.143641</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>1757376000000</v>
+        <v>1757289600000</v>
       </c>
       <c r="B151" t="n">
+        <v>37.9</v>
+      </c>
+      <c r="C151" t="n">
+        <v>38.17</v>
+      </c>
+      <c r="D151" t="n">
+        <v>36.46</v>
+      </c>
+      <c r="E151" t="n">
         <v>37.08</v>
       </c>
-      <c r="C151" t="n">
-        <v>37.9</v>
-      </c>
-      <c r="D151" t="n">
-        <v>36.73</v>
-      </c>
-      <c r="E151" t="n">
-        <v>37.36</v>
-      </c>
       <c r="F151" s="2" t="n">
-        <v>45909</v>
+        <v>45908</v>
       </c>
       <c r="G151" t="n">
-        <v>0.13957696</v>
+        <v>0.13749264</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>1757462400000</v>
+        <v>1757376000000</v>
       </c>
       <c r="B152" t="n">
+        <v>37.08</v>
+      </c>
+      <c r="C152" t="n">
+        <v>37.9</v>
+      </c>
+      <c r="D152" t="n">
+        <v>36.73</v>
+      </c>
+      <c r="E152" t="n">
         <v>37.36</v>
       </c>
-      <c r="C152" t="n">
-        <v>37.86</v>
-      </c>
-      <c r="D152" t="n">
-        <v>36.74</v>
-      </c>
-      <c r="E152" t="n">
-        <v>36.95</v>
-      </c>
       <c r="F152" s="2" t="n">
-        <v>45910</v>
+        <v>45909</v>
       </c>
       <c r="G152" t="n">
-        <v>0.13653025</v>
+        <v>0.13957696</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>1757548800000</v>
+        <v>1757462400000</v>
       </c>
       <c r="B153" t="n">
+        <v>37.36</v>
+      </c>
+      <c r="C153" t="n">
+        <v>37.86</v>
+      </c>
+      <c r="D153" t="n">
+        <v>36.74</v>
+      </c>
+      <c r="E153" t="n">
         <v>36.95</v>
       </c>
-      <c r="C153" t="n">
-        <v>37.03</v>
-      </c>
-      <c r="D153" t="n">
-        <v>35.26</v>
-      </c>
-      <c r="E153" t="n">
-        <v>35.26</v>
-      </c>
       <c r="F153" s="2" t="n">
-        <v>45911</v>
+        <v>45910</v>
       </c>
       <c r="G153" t="n">
-        <v>0.12432676</v>
+        <v>0.13653025</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>1757635200000</v>
+        <v>1757548800000</v>
       </c>
       <c r="B154" t="n">
+        <v>36.95</v>
+      </c>
+      <c r="C154" t="n">
+        <v>37.03</v>
+      </c>
+      <c r="D154" t="n">
         <v>35.26</v>
       </c>
-      <c r="C154" t="n">
-        <v>35.56</v>
-      </c>
-      <c r="D154" t="n">
-        <v>34.02</v>
-      </c>
       <c r="E154" t="n">
-        <v>34.66</v>
+        <v>35.26</v>
       </c>
       <c r="F154" s="2" t="n">
-        <v>45912</v>
+        <v>45911</v>
       </c>
       <c r="G154" t="n">
-        <v>0.12013156</v>
+        <v>0.12432676</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>1757721600000</v>
+        <v>1757635200000</v>
       </c>
       <c r="B155" t="n">
+        <v>35.26</v>
+      </c>
+      <c r="C155" t="n">
+        <v>35.56</v>
+      </c>
+      <c r="D155" t="n">
+        <v>34.02</v>
+      </c>
+      <c r="E155" t="n">
         <v>34.66</v>
       </c>
-      <c r="C155" t="n">
-        <v>34.79</v>
-      </c>
-      <c r="D155" t="n">
-        <v>34.19</v>
-      </c>
-      <c r="E155" t="n">
-        <v>34.28</v>
-      </c>
       <c r="F155" s="2" t="n">
-        <v>45913</v>
+        <v>45912</v>
       </c>
       <c r="G155" t="n">
-        <v>0.11751184</v>
+        <v>0.12013156</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>1757808000000</v>
+        <v>1757721600000</v>
       </c>
       <c r="B156" t="n">
+        <v>34.66</v>
+      </c>
+      <c r="C156" t="n">
+        <v>34.79</v>
+      </c>
+      <c r="D156" t="n">
+        <v>34.19</v>
+      </c>
+      <c r="E156" t="n">
         <v>34.28</v>
       </c>
-      <c r="C156" t="n">
-        <v>34.87</v>
-      </c>
-      <c r="D156" t="n">
-        <v>33.85</v>
-      </c>
-      <c r="E156" t="n">
-        <v>34.41</v>
-      </c>
       <c r="F156" s="2" t="n">
-        <v>45914</v>
+        <v>45913</v>
       </c>
       <c r="G156" t="n">
-        <v>0.11840481</v>
+        <v>0.11751184</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>1757894400000</v>
+        <v>1757808000000</v>
       </c>
       <c r="B157" t="n">
+        <v>34.28</v>
+      </c>
+      <c r="C157" t="n">
+        <v>34.87</v>
+      </c>
+      <c r="D157" t="n">
+        <v>33.85</v>
+      </c>
+      <c r="E157" t="n">
         <v>34.41</v>
       </c>
-      <c r="C157" t="n">
-        <v>35.98</v>
-      </c>
-      <c r="D157" t="n">
-        <v>34.26</v>
-      </c>
-      <c r="E157" t="n">
-        <v>35.56</v>
-      </c>
       <c r="F157" s="2" t="n">
-        <v>45915</v>
+        <v>45914</v>
       </c>
       <c r="G157" t="n">
-        <v>0.12645136</v>
+        <v>0.11840481</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>1757980800000</v>
+        <v>1757894400000</v>
       </c>
       <c r="B158" t="n">
+        <v>34.41</v>
+      </c>
+      <c r="C158" t="n">
+        <v>35.98</v>
+      </c>
+      <c r="D158" t="n">
+        <v>34.26</v>
+      </c>
+      <c r="E158" t="n">
         <v>35.56</v>
       </c>
-      <c r="C158" t="n">
-        <v>36.7</v>
-      </c>
-      <c r="D158" t="n">
-        <v>35.12</v>
-      </c>
-      <c r="E158" t="n">
-        <v>36.52</v>
-      </c>
       <c r="F158" s="2" t="n">
-        <v>45916</v>
+        <v>45915</v>
       </c>
       <c r="G158" t="n">
-        <v>0.13337104</v>
+        <v>0.12645136</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>1758067200000</v>
+        <v>1757980800000</v>
       </c>
       <c r="B159" t="n">
+        <v>35.56</v>
+      </c>
+      <c r="C159" t="n">
+        <v>36.7</v>
+      </c>
+      <c r="D159" t="n">
+        <v>35.12</v>
+      </c>
+      <c r="E159" t="n">
         <v>36.52</v>
       </c>
-      <c r="C159" t="n">
-        <v>37.45</v>
-      </c>
-      <c r="D159" t="n">
-        <v>34.99</v>
-      </c>
-      <c r="E159" t="n">
-        <v>35.55</v>
-      </c>
       <c r="F159" s="2" t="n">
-        <v>45917</v>
+        <v>45916</v>
       </c>
       <c r="G159" t="n">
-        <v>0.12638025</v>
+        <v>0.13337104</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>1758153600000</v>
+        <v>1758067200000</v>
       </c>
       <c r="B160" t="n">
+        <v>36.52</v>
+      </c>
+      <c r="C160" t="n">
+        <v>37.45</v>
+      </c>
+      <c r="D160" t="n">
+        <v>34.99</v>
+      </c>
+      <c r="E160" t="n">
         <v>35.55</v>
       </c>
-      <c r="C160" t="n">
-        <v>35.58</v>
-      </c>
-      <c r="D160" t="n">
-        <v>32.87</v>
-      </c>
-      <c r="E160" t="n">
-        <v>33.81</v>
-      </c>
       <c r="F160" s="2" t="n">
-        <v>45918</v>
+        <v>45917</v>
       </c>
       <c r="G160" t="n">
-        <v>0.11431161</v>
+        <v>0.12638025</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>1758240000000</v>
+        <v>1758153600000</v>
       </c>
       <c r="B161" t="n">
+        <v>35.55</v>
+      </c>
+      <c r="C161" t="n">
+        <v>35.58</v>
+      </c>
+      <c r="D161" t="n">
+        <v>32.87</v>
+      </c>
+      <c r="E161" t="n">
         <v>33.81</v>
       </c>
-      <c r="C161" t="n">
-        <v>35.6</v>
-      </c>
-      <c r="D161" t="n">
-        <v>33.4</v>
-      </c>
-      <c r="E161" t="n">
-        <v>34.78</v>
-      </c>
       <c r="F161" s="2" t="n">
-        <v>45919</v>
+        <v>45918</v>
       </c>
       <c r="G161" t="n">
-        <v>0.12096484</v>
+        <v>0.11431161</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>1758326400000</v>
+        <v>1758240000000</v>
       </c>
       <c r="B162" t="n">
+        <v>33.81</v>
+      </c>
+      <c r="C162" t="n">
+        <v>35.6</v>
+      </c>
+      <c r="D162" t="n">
+        <v>33.4</v>
+      </c>
+      <c r="E162" t="n">
         <v>34.78</v>
       </c>
-      <c r="C162" t="n">
-        <v>34.78</v>
-      </c>
-      <c r="D162" t="n">
-        <v>34.11</v>
-      </c>
-      <c r="E162" t="n">
-        <v>34.48</v>
-      </c>
       <c r="F162" s="2" t="n">
-        <v>45920</v>
+        <v>45919</v>
       </c>
       <c r="G162" t="n">
-        <v>0.11888704</v>
+        <v>0.12096484</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>1758412800000</v>
+        <v>1758326400000</v>
       </c>
       <c r="B163" t="n">
+        <v>34.78</v>
+      </c>
+      <c r="C163" t="n">
+        <v>34.78</v>
+      </c>
+      <c r="D163" t="n">
+        <v>34.11</v>
+      </c>
+      <c r="E163" t="n">
         <v>34.48</v>
       </c>
-      <c r="C163" t="n">
-        <v>34.62</v>
-      </c>
-      <c r="D163" t="n">
-        <v>34.06</v>
-      </c>
-      <c r="E163" t="n">
-        <v>34.51</v>
-      </c>
       <c r="F163" s="2" t="n">
-        <v>45921</v>
+        <v>45920</v>
       </c>
       <c r="G163" t="n">
-        <v>0.11909401</v>
+        <v>0.11888704</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>1758499200000</v>
+        <v>1758412800000</v>
       </c>
       <c r="B164" t="n">
+        <v>34.48</v>
+      </c>
+      <c r="C164" t="n">
+        <v>34.62</v>
+      </c>
+      <c r="D164" t="n">
+        <v>34.06</v>
+      </c>
+      <c r="E164" t="n">
         <v>34.51</v>
       </c>
-      <c r="C164" t="n">
-        <v>38.09</v>
-      </c>
-      <c r="D164" t="n">
-        <v>34.51</v>
-      </c>
-      <c r="E164" t="n">
-        <v>35.17</v>
-      </c>
       <c r="F164" s="2" t="n">
-        <v>45922</v>
+        <v>45921</v>
       </c>
       <c r="G164" t="n">
-        <v>0.12369289</v>
+        <v>0.11909401</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>1758585600000</v>
+        <v>1758499200000</v>
       </c>
       <c r="B165" t="n">
+        <v>34.51</v>
+      </c>
+      <c r="C165" t="n">
+        <v>38.09</v>
+      </c>
+      <c r="D165" t="n">
+        <v>34.51</v>
+      </c>
+      <c r="E165" t="n">
         <v>35.17</v>
       </c>
-      <c r="C165" t="n">
-        <v>37.17</v>
-      </c>
-      <c r="D165" t="n">
-        <v>35.09</v>
-      </c>
-      <c r="E165" t="n">
-        <v>37.14</v>
-      </c>
       <c r="F165" s="2" t="n">
-        <v>45923</v>
+        <v>45922</v>
       </c>
       <c r="G165" t="n">
-        <v>0.13793796</v>
+        <v>0.12369289</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>1758672000000</v>
+        <v>1758585600000</v>
       </c>
       <c r="B166" t="n">
+        <v>35.17</v>
+      </c>
+      <c r="C166" t="n">
+        <v>37.17</v>
+      </c>
+      <c r="D166" t="n">
+        <v>35.09</v>
+      </c>
+      <c r="E166" t="n">
         <v>37.14</v>
       </c>
-      <c r="C166" t="n">
-        <v>37.25</v>
-      </c>
-      <c r="D166" t="n">
-        <v>35.28</v>
-      </c>
-      <c r="E166" t="n">
-        <v>36.17</v>
-      </c>
       <c r="F166" s="2" t="n">
-        <v>45924</v>
+        <v>45923</v>
       </c>
       <c r="G166" t="n">
-        <v>0.13082689</v>
+        <v>0.13793796</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>1758758400000</v>
+        <v>1758672000000</v>
       </c>
       <c r="B167" t="n">
+        <v>37.14</v>
+      </c>
+      <c r="C167" t="n">
+        <v>37.25</v>
+      </c>
+      <c r="D167" t="n">
+        <v>35.28</v>
+      </c>
+      <c r="E167" t="n">
         <v>36.17</v>
       </c>
-      <c r="C167" t="n">
-        <v>37.98</v>
-      </c>
-      <c r="D167" t="n">
-        <v>35.68</v>
-      </c>
-      <c r="E167" t="n">
-        <v>37.69</v>
-      </c>
       <c r="F167" s="2" t="n">
-        <v>45925</v>
+        <v>45924</v>
       </c>
       <c r="G167" t="n">
-        <v>0.14205361</v>
+        <v>0.13082689</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>1758844800000</v>
+        <v>1758758400000</v>
       </c>
       <c r="B168" t="n">
+        <v>36.17</v>
+      </c>
+      <c r="C168" t="n">
+        <v>37.98</v>
+      </c>
+      <c r="D168" t="n">
+        <v>35.68</v>
+      </c>
+      <c r="E168" t="n">
         <v>37.69</v>
       </c>
-      <c r="C168" t="n">
-        <v>38.11</v>
-      </c>
-      <c r="D168" t="n">
-        <v>35.82</v>
-      </c>
-      <c r="E168" t="n">
-        <v>36.55</v>
-      </c>
       <c r="F168" s="2" t="n">
-        <v>45926</v>
+        <v>45925</v>
       </c>
       <c r="G168" t="n">
-        <v>0.13359025</v>
+        <v>0.14205361</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>1758931200000</v>
+        <v>1758844800000</v>
       </c>
       <c r="B169" t="n">
+        <v>37.69</v>
+      </c>
+      <c r="C169" t="n">
+        <v>38.11</v>
+      </c>
+      <c r="D169" t="n">
+        <v>35.82</v>
+      </c>
+      <c r="E169" t="n">
         <v>36.55</v>
       </c>
-      <c r="C169" t="n">
-        <v>36.87</v>
-      </c>
-      <c r="D169" t="n">
-        <v>36.35</v>
-      </c>
-      <c r="E169" t="n">
-        <v>36.42</v>
-      </c>
       <c r="F169" s="2" t="n">
-        <v>45927</v>
+        <v>45926</v>
       </c>
       <c r="G169" t="n">
-        <v>0.13264164</v>
+        <v>0.13359025</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>1759017600000</v>
+        <v>1758931200000</v>
       </c>
       <c r="B170" t="n">
+        <v>36.55</v>
+      </c>
+      <c r="C170" t="n">
+        <v>36.87</v>
+      </c>
+      <c r="D170" t="n">
+        <v>36.35</v>
+      </c>
+      <c r="E170" t="n">
         <v>36.42</v>
       </c>
-      <c r="C170" t="n">
-        <v>36.83</v>
-      </c>
-      <c r="D170" t="n">
-        <v>35.71</v>
-      </c>
-      <c r="E170" t="n">
-        <v>35.86</v>
-      </c>
       <c r="F170" s="2" t="n">
-        <v>45928</v>
+        <v>45927</v>
       </c>
       <c r="G170" t="n">
-        <v>0.12859396</v>
+        <v>0.13264164</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>1759104000000</v>
+        <v>1759017600000</v>
       </c>
       <c r="B171" t="n">
+        <v>36.42</v>
+      </c>
+      <c r="C171" t="n">
+        <v>36.83</v>
+      </c>
+      <c r="D171" t="n">
+        <v>35.71</v>
+      </c>
+      <c r="E171" t="n">
         <v>35.86</v>
       </c>
-      <c r="C171" t="n">
-        <v>36.96</v>
-      </c>
-      <c r="D171" t="n">
-        <v>35.21</v>
-      </c>
-      <c r="E171" t="n">
-        <v>36.39</v>
-      </c>
       <c r="F171" s="2" t="n">
-        <v>45929</v>
+        <v>45928</v>
       </c>
       <c r="G171" t="n">
-        <v>0.13242321</v>
+        <v>0.12859396</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>1759190400000</v>
+        <v>1759104000000</v>
       </c>
       <c r="B172" t="n">
+        <v>35.86</v>
+      </c>
+      <c r="C172" t="n">
+        <v>36.96</v>
+      </c>
+      <c r="D172" t="n">
+        <v>35.21</v>
+      </c>
+      <c r="E172" t="n">
         <v>36.39</v>
       </c>
-      <c r="C172" t="n">
-        <v>37.06</v>
-      </c>
-      <c r="D172" t="n">
-        <v>35.64</v>
-      </c>
-      <c r="E172" t="n">
-        <v>36.61</v>
-      </c>
       <c r="F172" s="2" t="n">
-        <v>45930</v>
+        <v>45929</v>
       </c>
       <c r="G172" t="n">
-        <v>0.13402921</v>
+        <v>0.13242321</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>1759276800000</v>
+        <v>1759190400000</v>
       </c>
       <c r="B173" t="n">
+        <v>36.39</v>
+      </c>
+      <c r="C173" t="n">
+        <v>37.06</v>
+      </c>
+      <c r="D173" t="n">
+        <v>35.64</v>
+      </c>
+      <c r="E173" t="n">
         <v>36.61</v>
       </c>
-      <c r="C173" t="n">
-        <v>37.7</v>
-      </c>
-      <c r="D173" t="n">
-        <v>35.9</v>
-      </c>
-      <c r="E173" t="n">
-        <v>37.12</v>
-      </c>
       <c r="F173" s="2" t="n">
-        <v>45931</v>
+        <v>45930</v>
       </c>
       <c r="G173" t="n">
-        <v>0.13778944</v>
+        <v>0.13402921</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>1759363200000</v>
+        <v>1759276800000</v>
       </c>
       <c r="B174" t="n">
+        <v>36.61</v>
+      </c>
+      <c r="C174" t="n">
+        <v>37.7</v>
+      </c>
+      <c r="D174" t="n">
+        <v>35.9</v>
+      </c>
+      <c r="E174" t="n">
         <v>37.12</v>
       </c>
-      <c r="C174" t="n">
-        <v>37.9</v>
-      </c>
-      <c r="D174" t="n">
-        <v>36.74</v>
-      </c>
-      <c r="E174" t="n">
-        <v>37.39</v>
-      </c>
       <c r="F174" s="2" t="n">
-        <v>45932</v>
+        <v>45931</v>
       </c>
       <c r="G174" t="n">
-        <v>0.13980121</v>
+        <v>0.13778944</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>1759449600000</v>
+        <v>1759363200000</v>
       </c>
       <c r="B175" t="n">
+        <v>37.12</v>
+      </c>
+      <c r="C175" t="n">
+        <v>37.9</v>
+      </c>
+      <c r="D175" t="n">
+        <v>36.74</v>
+      </c>
+      <c r="E175" t="n">
         <v>37.39</v>
       </c>
-      <c r="C175" t="n">
-        <v>38.96</v>
-      </c>
-      <c r="D175" t="n">
-        <v>36.81</v>
-      </c>
-      <c r="E175" t="n">
-        <v>38.03</v>
-      </c>
       <c r="F175" s="2" t="n">
-        <v>45933</v>
+        <v>45932</v>
       </c>
       <c r="G175" t="n">
-        <v>0.14462809</v>
+        <v>0.13980121</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>1759536000000</v>
+        <v>1759449600000</v>
       </c>
       <c r="B176" t="n">
-        <v>38.03</v>
+        <v>37.39</v>
       </c>
       <c r="C176" t="n">
-        <v>38.29</v>
+        <v>38.96</v>
       </c>
       <c r="D176" t="n">
-        <v>37.49</v>
+        <v>36.81</v>
       </c>
       <c r="E176" t="n">
         <v>38.03</v>
       </c>
       <c r="F176" s="2" t="n">
-        <v>45934</v>
+        <v>45933</v>
       </c>
       <c r="G176" t="n">
         <v>0.14462809</v>
@@ -4496,140 +4496,140 @@
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>1759622400000</v>
+        <v>1759536000000</v>
       </c>
       <c r="B177" t="n">
         <v>38.03</v>
       </c>
       <c r="C177" t="n">
-        <v>39.66</v>
+        <v>38.29</v>
       </c>
       <c r="D177" t="n">
-        <v>37.92</v>
+        <v>37.49</v>
       </c>
       <c r="E177" t="n">
-        <v>37.95</v>
+        <v>38.03</v>
       </c>
       <c r="F177" s="2" t="n">
-        <v>45935</v>
+        <v>45934</v>
       </c>
       <c r="G177" t="n">
-        <v>0.14402025</v>
+        <v>0.14462809</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="n">
-        <v>1759708800000</v>
+        <v>1759622400000</v>
       </c>
       <c r="B178" t="n">
+        <v>38.03</v>
+      </c>
+      <c r="C178" t="n">
+        <v>39.66</v>
+      </c>
+      <c r="D178" t="n">
+        <v>37.92</v>
+      </c>
+      <c r="E178" t="n">
         <v>37.95</v>
       </c>
-      <c r="C178" t="n">
-        <v>39.42</v>
-      </c>
-      <c r="D178" t="n">
-        <v>37.67</v>
-      </c>
-      <c r="E178" t="n">
-        <v>39.26</v>
-      </c>
       <c r="F178" s="2" t="n">
-        <v>45936</v>
+        <v>45935</v>
       </c>
       <c r="G178" t="n">
-        <v>0.15413476</v>
+        <v>0.14402025</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>1759795200000</v>
+        <v>1759708800000</v>
       </c>
       <c r="B179" t="n">
-        <v>39.07</v>
+        <v>37.95</v>
       </c>
       <c r="C179" t="n">
-        <v>39.39</v>
+        <v>39.42</v>
       </c>
       <c r="D179" t="n">
-        <v>38.54</v>
+        <v>37.67</v>
       </c>
       <c r="E179" t="n">
-        <v>39.28</v>
+        <v>39.26</v>
       </c>
       <c r="F179" s="2" t="n">
-        <v>45937</v>
+        <v>45936</v>
       </c>
       <c r="G179" t="n">
-        <v>0.15429184</v>
+        <v>0.15413476</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="n">
-        <v>1759881600000</v>
+        <v>1759795200000</v>
       </c>
       <c r="B180" t="n">
-        <v>39.28</v>
+        <v>39.07</v>
       </c>
       <c r="C180" t="n">
-        <v>40.03</v>
+        <v>39.39</v>
       </c>
       <c r="D180" t="n">
         <v>38.54</v>
       </c>
       <c r="E180" t="n">
-        <v>39.44</v>
+        <v>39.28</v>
       </c>
       <c r="F180" s="2" t="n">
-        <v>45938</v>
+        <v>45937</v>
       </c>
       <c r="G180" t="n">
-        <v>0.15555136</v>
+        <v>0.15429184</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="n">
-        <v>1759968000000</v>
+        <v>1759881600000</v>
       </c>
       <c r="B181" t="n">
+        <v>39.28</v>
+      </c>
+      <c r="C181" t="n">
+        <v>40.03</v>
+      </c>
+      <c r="D181" t="n">
+        <v>38.54</v>
+      </c>
+      <c r="E181" t="n">
         <v>39.44</v>
       </c>
-      <c r="C181" t="n">
-        <v>40.44</v>
-      </c>
-      <c r="D181" t="n">
-        <v>39.33</v>
-      </c>
-      <c r="E181" t="n">
-        <v>39.73</v>
-      </c>
       <c r="F181" s="2" t="n">
-        <v>45939</v>
+        <v>45938</v>
       </c>
       <c r="G181" t="n">
-        <v>0.15784729</v>
+        <v>0.15555136</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>1760054400000</v>
+        <v>1759968000000</v>
       </c>
       <c r="B182" t="n">
+        <v>39.44</v>
+      </c>
+      <c r="C182" t="n">
+        <v>40.44</v>
+      </c>
+      <c r="D182" t="n">
+        <v>39.33</v>
+      </c>
+      <c r="E182" t="n">
         <v>39.73</v>
       </c>
-      <c r="C182" t="n">
-        <v>64.88</v>
-      </c>
-      <c r="D182" t="n">
-        <v>39.45</v>
-      </c>
-      <c r="E182" t="n">
-        <v>44.11</v>
-      </c>
       <c r="F182" s="2" t="n">
-        <v>45940</v>
+        <v>45939</v>
       </c>
       <c r="G182" t="n">
-        <v>0.19456921</v>
+        <v>0.15784729</v>
       </c>
     </row>
   </sheetData>
